--- a/untitled folder/HSC_Physics_2nd_Paper_Chapter_08_Introduction_to_Modern_Physics.xlsx
+++ b/untitled folder/HSC_Physics_2nd_Paper_Chapter_08_Introduction_to_Modern_Physics.xlsx
@@ -1168,11 +1168,6 @@
           <t>একটি জড় প্রসঙ্গ কাঠামো (Inertial frame) এবং একটি অজড় প্রসঙ্গ কাঠামোর (Non-inertial frame) মধ্যে নিউটনের প্রথম ও দ্বিতীয় গতিসূত্রের বৈধতার মৌলিক পার্থক্য কী? অজড় কাঠামোতে নিউটনের সূত্র প্রয়োগ করতে কোন বল বিবেচনা করতে হয়?</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>জড় প্রসঙ্গ কাঠামো হলো এমন একটি কাঠামো যা স্থির থাকে অথবা ধ্রুব বেগে গতিশীল (ত্বরণ শূন্য, $a = 0$), যেখানে নিউটনের গতিসূত্রগুলো কোনো বাহ্যিক সংশোধন ছাড়াই সরাসরি কার্যকর হয়। অজড় প্রসঙ্গ কাঠামো হলো ত্বরিত বা ঘূর্ণায়মান কাঠামো ($a \neq 0$), যেখানে কোনো বাহ্যিক বল ছাড়াই বস্তুর ত্বরণ অনুভূত হয়। ফলে নিউটনের সূত্র বৈধ রাখতে কাঠামোটির ত্বরণের বিপরীতমুখী একটি কাল্পনিক বা জড়তা বল (Pseudo force বা Inertial force, $\vec{F}_{\text{pseudo}} = -m\vec{a}_0$) বিবেচনা করতে হয়।</t>
@@ -1218,11 +1213,6 @@
           <t>ক্লাসিক্যাল মেকানিক্সে স্থান ও কালকে পরম ধরে প্রাপ্ত গ্যালিলীয় রূপান্তরের (Galilean transformation) অধীনে আলো ও তড়িৎ-চৌম্বকীয় তরঙ্গ সম্পর্কিত ম্যাক্সওয়েলের সমীকরণগুলো নিশ্চল বা অপরিবর্তিত (Invariant) থাকে না কেন?</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>গ্যালিলীয় রূপান্তর বেগ সংযোজন সূত্রের মাধ্যমে নির্দেশ করে যে এক কাঠামোর বেগ $u$ হলে অপর গতিশীল কাঠামোতে আলোর বেগ হবে $c' = c \pm v$। কিন্তু ম্যাক্সওয়েলের তরঙ্গ সমীকরণ থেকে প্রাপ্ত আলোর বেগ $c = \frac{1}{\sqrt{\mu_0 \epsilon_0}}$ একটি বিশ্বজনীন সার্বজনীন ধ্রুবক যা কোনো গতিশীল ব্যবস্থার বেগের ওপর নির্ভর করে না। ফলে গ্যালিলীয় রূপান্তর প্রয়োগ করলে ম্যাক্সওয়েল সমীকরণের রূপ পরিবর্তিত হয়ে যায়, যা নির্দেশ করে যে স্থান ও কালের ক্লাসিক্যাল গ্যালিলীয় ধারণা তড়িৎগতিবিদ্যার ক্ষেত্রে সঠিক নয়।</t>
@@ -1268,11 +1258,6 @@
           <t>মাইকেলসন-মর্লি (Michelson-Morley) পরীক্ষার মূল ঐতিহাসিক উদ্দেশ্য কী ছিল এবং তাত্ত্বিকভাবে তারা কোন মাধ্যমে পৃথিবীর আপেক্ষিক গতি নির্ণয় করতে চেয়েছিলেন?</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>ঊনবিংশ শতাব্দীতে বিশ্বাস করা হতো মহাবিশ্ব জুড়ে 'আলোকবাহী ইথার' (Luminiferous aether) নামক একটি পরম স্থির, স্থিতিস্থাপক ও ঘর্ষণহীন মাধ্যম বিদ্যমান যার সাপেক্ষে আলোর বেগ $c$। মাইকেলসন-মর্লি পরীক্ষার উদ্দেশ্য ছিল নিজ কক্ষপথে ঘূর্ণায়মান পৃথিবীর সাপেক্ষে ইথার মাধ্যমের আপেক্ষিক বায়ু প্রবাহ (Ether wind) বা পৃথিবীর পরম গতি নির্ণয় করা।</t>
@@ -1318,11 +1303,6 @@
           <t>মাইকেলসন-মর্লি পরীক্ষায় সমদৈর্ঘ্য $L$-এর দুটি লম্ব বাহুতে ইথারের গতিবেগ $v$ ধরে সমান্তরাল ও লম্ব বরাবর আলোর যাতায়াতে তাত্ত্বিক সময় পার্থক্যের সমীকরণ $v \ll c$-এর জন্য কী রূপ দাঁড়ায়?</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>ইথারের প্রবাহের সমান্তরাল বাহুতে আলোর যাতায়াতের সময় $t_{\parallel} = \frac{L}{c-v} + \frac{L}{c+v} = \frac{2Lc}{c^2 - v^2} = \frac{2L}{c(1 - v^2/c^2)}$। লম্ব বাহুতে যাতায়াতের সময় $t_{\perp} = \frac{2L}{\sqrt{c^2 - v^2}} = \frac{2L}{c\sqrt{1 - v^2/c^2}}$। সময় পার্থক্য $\Delta t = t_{\parallel} - t_{\perp} \approx \frac{2L}{c}\left[\left(1 + \frac{v^2}{c^2}\right) - \left(1 + \frac{v^2}{2c^2}\right)\right] = \frac{L v^2}{c^3}$।</t>
@@ -1368,11 +1348,6 @@
           <t>যন্ত্রটিকে $90^\circ$ ঘোরালেও কোনো প্রত্যাশিত ব্যতিচার ডোরার সরণ (Fringe shift) দেখা যায়নি। এই 'নেতিবাচক ফলাফল' (Null result) পদার্থবিজ্ঞানে কোন যুগান্তকারী সিদ্ধান্তে উপনীত করে?</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>পরীক্ষার প্রত্যাশিত ডোরার সরণ ছিল $\Delta N = \frac{2L v^2}{\lambda c^2} \approx 0.4$ ডোরা, কিন্তু বাস্তবে কোনো সরণ পরিলক্ষিত হয়নি ($\Delta N = 0$)। এই নেতিবাচক ফলাফল প্রমাণ করে যে: (১) ইথার বলে কোনো পরম মাধ্যমের অস্তিত্ব নেই, (২) কোনো পরম প্রসঙ্গ কাঠামোর অস্তিত্ব নেই, এবং (৩) সকল জড় কাঠামোতে শূন্য মাধ্যমে আলোর বেগ সর্বদা ধ্রুব ও পর্যবেক্ষকের গতির ওপর সম্পূর্ণ স্বাধীন।</t>
@@ -1418,11 +1393,6 @@
           <t>মাইকেলসন-মর্লি পরীক্ষার ফলাফল ব্যাখ্যায় 'সম্পূর্ণ ইথার ড্র্যাগ হাইপোথিসিস' (Complete Ether Drag Hypothesis) কেন গ্রহণযোগ্য হয়নি? কোন জ্যোতির্বৈজ্ঞানিক পর্যবেক্ষণ এর বিরোধিতা করে?</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>ইথার ড্র্যাগ প্রস্তাবে বলা হয়েছিল পৃথিবী গতিশীল থাকার সময় তার চারপাশের ইথারকে সাথে টেনে নিয়ে যায়, ফলে ভূপৃষ্ঠে কোনো আপেক্ষিক ইথার বাতাস পাওয়া যায় না। কিন্তু যদি পৃথিবী ইথার টেনে নিত, তবে দূরবর্তী নক্ষত্র থেকে আগত আলোর ক্ষেত্রে 'নাক্ষত্রিক অপেরণ' (Stellar Aberration - যা ব্র্যাডলি ১৭২৭ সালে পর্যবেক্ষণ করেছিলেন) ঘটা অসম্ভব হতো। অপেরণ সুস্পষ্টভাবে প্রমাণ করে যে পৃথিবী ইথার টেনে নিয়ে চলে না, ফলে এই হাইপোথিসিস বাতিল হয়ে যায়।</t>
@@ -1468,11 +1438,6 @@
           <t>ক্লাসিক্যাল শব্দের ডপলার ক্রিয়ার ক্ষেত্রে উৎস গতিশীল হওয়া এবং পর্যবেক্ষক গতিশীল হওয়ার ফলাফল ভিন্ন হয় কেন, অথচ আলোর ক্ষেত্রে তা কেবল তাদের আপেক্ষিক বেগের ওপর নির্ভর করে কেন?</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>শব্দ তরঙ্গের সঞ্চালনের জন্য একটি বাস্তব মাধ্যম (বায়ু) প্রয়োজন। ফলে মাধ্যমটির সাপেক্ষে উৎসের গতি এবং পর্যবেক্ষকের গতির ভৌত প্রভাব পৃথক হয়। কিন্তু আলোর ক্ষেত্রে কোনো মাধ্যমের প্রয়োজন নেই এবং শূন্য মাধ্যমে আলোর বেগ ধ্রুবক। বিশেষ আপেক্ষিকতা অনুসারে আলোর ডপলার ক্রিয়া কোনো মাধ্যমের সাপেক্ষে নয়, বরং কেবল উৎস ও পর্যবেক্ষকের মধ্যকার সরাসরি আপেক্ষিক বেগ $\beta = v/c$-এর ওপর নির্ভরশীল।</t>
@@ -1518,11 +1483,6 @@
           <t>$S$ কাঠামোর সাপেক্ষে $S'$ কাঠামো $X$-অক্ষ বরাবর ধ্রুব বেগ $v$-তে গতিশীল হলে গ্যালিলীয় রূপান্তরের সমীকরণসমূহ এবং সময়ের রূপান্তরের প্রকৃতি কী?</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>ক্লাসিক্যাল মেকানিক্সে সময় পরম ($t' = t$)। গ্যালিলীয় রূপান্তর সমীকরণ: $x' = x - vt$, $y' = y$, $z' = z$, $t' = t$। বিপরীত রূপান্তর: $x = x' + vt'$, $y = y'$, $z = z'$, $t = t'$। এখানে স্থান ও কালকে সম্পূর্ণ স্বাধীন ও অসংযুক্ত সত্ত্বা হিসেবে বিবেচনা করা হয়।</t>
@@ -1568,11 +1528,6 @@
           <t>একটি নক্ষত্র সরাসরি মাথার উপর (উল্লম্বভাবে) অবস্থিত। পৃথিবী $v$ বেগে কক্ষপথে গতিশীল হলে দূরবীক্ষণ যন্ত্রকে উল্লম্বের সাথে কত অপেরণ কোণ $\theta$-তে হেলাতে হবে? ($v \ll c$)</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>নক্ষত্রের আলোর বেগ উল্লম্বভাবে নিচের দিকে $c$ এবং পৃথিবীর বেগ অনুভূমিকভাবে $v$। দূরবীক্ষণ যন্ত্রের সাথে আলোর আপেক্ষিক বেগ নির্ণয় করতে ভেক্টর বিয়োগ করলে আপেক্ষিক বেগ হবে $\vec{c}' = \vec{c} - \vec{v}$। উল্লম্বের সাথে উৎপন্ন কোণ $\tan\theta = \frac{v}{c}$। যেহেতু $v \ll c$, তাই ক্ষুদ্র কোণের জন্য অপেরণ কোণ $\theta \approx \frac{v}{c}$ রেডিয়ান।</t>
@@ -1618,11 +1573,6 @@
           <t>ফিজিউ (Fizeau) প্রবাহিত পানিতে আলোর বেগ মেপে দেখেছিলেন $v_{\text{obs}} = \frac{c}{\mu} + v\left(1 - \frac{1}{\mu^2}\right)$। ফ্রেনেলের এই ইথার ড্র্যাগিং গুণক $\left(1 - \frac{1}{\mu^2}\right)$ আপেক্ষিকতার কোন সূত্র থেকে প্রাকৃতিকভাবে প্রতিপাদিত হয়?</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>আইনস্টাইনের আপেক্ষিকীয় বেগ সংযোজন সূত্র: $u = \frac{u' + v}{1 + \frac{u' v}{c^2}}$। এখানে পানিতে আলোর বেগ $u' = \frac{c}{\mu}$। মান বসালে: $u = \frac{c/\mu + v}{1 + \frac{v}{\mu c}} \approx \left(\frac{c}{\mu} + v\right)\left(1 - \frac{v}{\mu c}\right) = \frac{c}{\mu} + v - \frac{v}{\mu^2} = \frac{c}{\mu} + v\left(1 - \frac{1}{\mu^2}\right)$। অর্থাৎ কোনো ইথারের অস্তিত্ব ছাড়াই আপেক্ষিকীয় বেগ সংযোজন থেকে ফ্রেনেলের গুণকটি নিখুঁতভাবে বেরিয়ে আসে।</t>
@@ -1668,11 +1618,6 @@
           <t>১৯০৫ সালে আলবার্ট আইনস্টাইন কর্তৃক প্রস্তাবিত বিশেষ আপেক্ষিকতা তত্ত্বের (Special Theory of Relativity - STR) দুটি মৌলিক স্বীকার্য স্পষ্টভাবে বিবৃত করো।</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>স্বীকার্য ১ (আপেক্ষিকতার নীতি - Principle of Relativity): সমস্ত জড় প্রসঙ্গ কাঠামোতে পদার্থবিজ্ঞানের মৌলিক সূত্রগুলো অভিন্ন বা অপরিবর্তিত থাকে। স্বীকার্য ২ (আলোর বেগের ধ্রুবতা - Constancy of the Speed of Light): শূন্য মাধ্যমে আলোর দ্রুতি ($c$) সমস্ত জড় প্রসঙ্গ কাঠামোতে সর্বদা একই থাকে, যা আলোক উৎসের বা পর্যবেক্ষকের গতির ওপর সম্পূর্ণ স্বাধীন।</t>
@@ -1718,11 +1663,6 @@
           <t>$S$ কাঠামোর সাপেক্ষে $S'$ কাঠামো $X$-অক্ষ বরাবর $v$ বেগে গতিশীল। স্থান ও কালের স্থানাঙ্কের লরেন্টজ রূপান্তর সমীকরণসমূহ লেখো এবং এতে ব্যবহৃত লরেন্টজ ফ্যাক্টর $\gamma$-এর সংজ্ঞা দাও।</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>লরেন্টজ রূপান্তর সমীকরণ: $x' = \gamma (x - vt)$, $y' = y$, $z' = z$, এবং $t' = \gamma \left(t - \frac{vx}{c^2}\right)$। এখানে লরেন্টজ ফ্যাক্টর $\gamma = \frac{1}{\sqrt{1 - \frac{v^2}{c^2}}} = \frac{1}{\sqrt{1 - \beta^2}}$ যেখানে $\beta = \frac{v}{c}$। বিপরীত রূপান্তরের ক্ষেত্রে কেবল $v$-এর স্থলে $-v$ প্রতিস্থাপিত হয়।</t>
@@ -1768,11 +1708,6 @@
           <t>কোন সীমামূলক শর্তে (Limiting condition) লরেন্টজ রূপান্তর সমীকরণসমূহ হুবহু ক্লাসিক্যাল গ্যালিলীয় রূপান্তর সমীকরণে রূপান্তরিত হয়?</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>যখন কোনো বস্তুর আপেক্ষিক বেগ আলোর বেগ অপেক্ষা অত্যন্ত নগণ্য হয় ($v \ll c$ বা $\frac{v}{c} \to 0$ অথবা গাণিতিক সীমায় $c \to \infty$): তখন $\frac{v^2}{c^2} \to 0 \Rightarrow \gamma = \frac{1}{\sqrt{1-0}} = 1$। ফলে $x' = 1 \cdot (x - vt) = x - vt$ এবং $t' = 1 \cdot \left(t - 0\right) = t$। এভাবে লরেন্টজ সমীকরণ ক্লাসিক্যাল গ্যালিলীয় সমীকরণে নেমে আসে, যা প্রমাণ করে ক্লাসিক্যাল মেকানিক্স হলো আপেক্ষিকতার একটি বিশেষ নিম্নগতির রূপ।</t>
@@ -1818,11 +1753,6 @@
           <t>$S$ কাঠামোতে দুটি ভিন্ন স্থানে ($x_1 \neq x_2$) একই সময়ে ($t_1 = t_2$) দুটি ঘটনা সংঘটিত হলো। $v$ বেগে গতিশীল $S'$ কাঠামোতে ঘটনা দুটি কি এককালীন হবে? তাদের সময়ের পার্থক্য $\Delta t'$ কত হবে?</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>লরেন্টজ রূপান্তর অনুযায়ী $t' = \gamma \left(t - \frac{vx}{c^2}\right)$। সময় পার্থক্য: $\Delta t' = t_2' - t_1' = \gamma \left((t_2 - t_1) - \frac{v(x_2 - x_1)}{c^2}\right)$। যেহেতু $t_1 = t_2 \Rightarrow \Delta t = 0$, সুতরাং $\Delta t' = -\frac{\gamma v}{c^2}(x_2 - x_1) \neq 0$। অর্থাৎ এক কাঠামোতে এককালীন হলেও স্থান ভিন্ন হওয়ায় অপর গতিশীল কাঠামোতে ঘটনা দুটি এককালীন হবে না। এটিই এককালিনতার আপেক্ষিকতা।</t>
@@ -1868,11 +1798,6 @@
           <t>একটি মহাশূন্যযান পৃথিবীর সাপেক্ষে $0.8c$ বেগে চলছে। যানটি তার গতির অভিমুখে পৃথিবীর সাপেক্ষে বিপরীত দিকে নয়, সামনের দিকে $0.6c$ বেগে একটি প্রোব নিক্ষেপ করল। পৃথিবীর পর্যবেক্ষকের সাপেক্ষে প্রোবটির বেগ কত হবে?</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>আইনস্টাইনের বেগ সংযোজন সূত্র: $u = \frac{u' + v}{1 + \frac{u' v}{c^2}}$। এখানে যানটির বেগ $v = 0.8c$ এবং যানের সাপেক্ষে প্রোবের বেগ $u' = 0.6c$। মান বসিয়ে: $u = \frac{0.6c + 0.8c}{1 + \frac{(0.6c)(0.8c)}{c^2}} = \frac{1.4c}{1 + 0.48} = \frac{1.4}{1.48} c = \frac{140}{148} c = \frac{35}{37} c \approx 0.946c$। বেগ কখনো $c$ অতিক্রম করে না।</t>
@@ -1918,11 +1843,6 @@
           <t>দুটি ফোটন পরস্পর বিপরীত দিকে আলোর বেগে ($c$) গতিশীল। একটি ফোটনের সাপেক্ষে অপর ফোটনটির আপেক্ষিক বেগ কত?</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>একটি ফোটনের সাপেক্ষে অপরটির বেগ বের করতে বেগ সংযোজন সূত্র ব্যবহার করতে হবে: $u = \frac{u' + v}{1 + \frac{u' v}{c^2}}$। এখানে $v = c$ এবং $u' = c$। তাহলে $u = \frac{c + c}{1 + \frac{c \cdot c}{c^2}} = \frac{2c}{1 + 1} = \frac{2c}{2} = c$। ক্লাসিক্যাল নিয়মে $c - (-c) = 2c$ মনে হলেও আপেক্ষিকতায় কোনো গতিশীল কাঠামোর সাপেক্ষেই আলোর বেগ $c$ অতিক্রম করে না, সর্বদা $c$-ই থাকে।</t>
@@ -1968,11 +1888,6 @@
           <t>স্থান-কালের যে কোনো দুটি ঘটনার জন্য চার-মাত্রিক ব্যবধান $\Delta s^2 = c^2 \Delta t^2 - \Delta x^2 - \Delta y^2 - \Delta z^2$। প্রমাণ করো যে এটি লরেন্টজ রূপান্তরের অধীনে একটি ইনভেরিয়েন্ট (Invariant বা নিশ্চল) রাশি।</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>লরেন্টজ রূপান্তর বসালে: $c^2 \Delta t'^2 - \Delta x'^2 = c^2 \gamma^2 \left(\Delta t - \frac{v \Delta x}{c^2}\right)^2 - \gamma^2 (\Delta x - v \Delta t)^2$। বিস্তার করলে: $\gamma^2 \left[c^2 \Delta t^2 - 2v \Delta x \Delta t + \frac{v^2 \Delta x^2}{c^2} - (\Delta x^2 - 2v \Delta x \Delta t + v^2 \Delta t^2)\right] = \gamma^2 \left[(c^2 - v^2)\Delta t^2 - \left(1 - \frac{v^2}{c^2}\right)\Delta x^2\right] = \gamma^2 (1 - \frac{v^2}{c^2})[c^2 \Delta t^2 - \Delta x^2] = 1 \cdot [c^2 \Delta t^2 - \Delta x^2]$। যেহেতু $\Delta y' = \Delta y, \Delta z' = \Delta z$, সুতরাং $\Delta s'^2 = \Delta s^2$।</t>
@@ -2018,11 +1933,6 @@
           <t>$S'$ কাঠামোতে একটি আলোর সংকেত $Y'$-অক্ষ বরাবর $c$ বেগে নির্গত হলো ($u_x' = 0, u_y' = c$)। $S$ কাঠামোর সাপেক্ষে $S'$ কাঠামো $X$-অক্ষ বরাবর $v$ বেগে চললে $S$ কাঠামোতে আলোর লব্ধি বেগ কত হবে?</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>তির্যক বেগ রূপান্তর সমীকরণ: $u_x = \frac{u_x' + v}{1 + \frac{u_x' v}{c^2}} = \frac{0 + v}{1 + 0} = v$। এবং $u_y = \frac{u_y'}{\gamma\left(1 + \frac{u_x' v}{c^2}\right)} = \frac{c}{\gamma(1 + 0)} = c \sqrt{1 - \frac{v^2}{c^2}}$। লব্ধি বেগ $u = \sqrt{u_x^2 + u_y^2} = \sqrt{v^2 + c^2\left(1 - \frac{v^2}{c^2}\right)} = \sqrt{v^2 + c^2 - v^2} = \sqrt{c^2} = c$। অর্থাৎ যেকোনো দিকেই লব্ধি বেগ আলোর বেগ $c$-এর সমান থাকে।</t>
@@ -2068,11 +1978,6 @@
           <t>বিশেষ আপেক্ষিকতায় কোনো সংকেত বা তথ্য প্রেরণের গতি আলোর গতি $c$-এর বেশি ($v &gt; c$) হতে পারে না কেন? এর সাথে কার্যকারণ নীতির (Principle of Causality) সম্পর্ক কী?</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>যদি কোনো সংকেতের গতি $u &gt; c$ হতো, তবে এমন একটি জড় কাঠামো $S'$ খুঁজে পাওয়া সম্ভব যেখানে $\Delta t' = \gamma \left(\Delta t - \frac{u v \Delta t}{c^2}\right) = \gamma \Delta t \left(1 - \frac{u v}{c^2}\right) &lt; 0$ হবে (যখন $v &gt; c^2/u$)। এর অর্থ কারণ ঘটার আগেই ফলাফল ঘটে যাবে (সংকেত পৌঁছার পর সংকেত পাঠানো হবে)। কার্যকারণ নীতি বা মহাবিশ্বের কার্য-কারণ সম্পর্কের সার্বজনীনতা রক্ষার জন্য তথ্যের গতি $c$-এর মধ্যে সীমাবদ্ধ থাকা বাধ্যতামূলক।</t>
@@ -2169,11 +2074,6 @@
           <t>সঠিক সময় (Proper time) $t_0$ বলতে কী বোঝায়? স্থির পর্যবেক্ষকের সাপেক্ষে $v$ বেগে গতিশীল একটি ঘড়ির জন্য পরিমাপকৃত সময় $t$-এর সমীকরণটি লেখো এবং $t &gt; t_0$ হওয়ার তাৎপর্য ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>সঠিক সময় ($t_0$) হলো সেই সময় ব্যবধান যা এমন একটি ঘড়ি দ্বারা পরিমাপ করা হয় যা দুটি ঘটনার স্থানেই স্থির থাকে (অর্থাৎ একই স্থানিক অবস্থানে ঘটা দুটি ঘটনার মধ্যকার সময়)। যে পর্যবেক্ষকের সাপেক্ষে ঘড়িটি $v$ বেগে গতিশীল, তার কাছে পরিমাপকৃত সময় $t = \frac{t_0}{\sqrt{1 - \frac{v^2}{c^2}}} = \gamma t_0$। যেহেতু $\gamma &gt; 1$, তাই $t &gt; t_0$ হয়। এর অর্থ হলো গতিশীল ঘড়ি ধীরগতিতে চলে (Moving clocks run slow), যা কাল দীর্ঘায়ন বা সময় প্রসারণ নামে পরিচিত।</t>
@@ -2219,11 +2119,6 @@
           <t>ভূপৃষ্ঠ থেকে $10\text{ km}$ উঁচুতে সৃষ্টি হওয়া মিউয়ন কণার নিশ্চল জীবনকাল $\tau_0 = 2.2\ \mu\text{s}$। ক্লাসিক্যাল হিসাবে এটি আলো বেগে চললেও ভূপৃষ্ঠে পৌঁছাতে পারে না, কিন্তু $v = 0.998c$ বেগে চললে কেন এটি প্রচুর পরিমাণে ভূপৃষ্ঠে পৌঁছায়?</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>ক্লাসিক্যাল মেকানিক্সে মিউয়নের অতিক্রান্ত দূরত্ব $s = c \tau_0 = 3 \times 10^8 \times 2.2 \times 10^{-6}\text{ m} \approx 660\text{ m} \ll 10\text{ km}$। কিন্তু $v = 0.998c$ বেগে লরেন্টজ ফ্যাক্টর $\gamma = \frac{1}{\sqrt{1 - 0.998^2}} \approx \frac{1}{\sqrt{0.003996}} \approx 15.8$। পৃথিবীর পর্যবেক্ষকের সাপেক্ষে মিউয়নের প্রসারিত জীবনকাল $t = \gamma \tau_0 \approx 15.8 \times 2.2\ \mu\text{s} \approx 34.8\ \mu\text{s}$। এই সময়ে মিউয়নের অতিক্রান্ত পথ $s' = v t \approx 0.998 \times 3 \times 10^8 \times 34.8 \times 10^{-6}\text{ m} \approx 10.4\text{ km} &gt; 10\text{ km}$। ফলে এটি সহজে ভূপৃষ্ঠে পৌঁছায়।</t>
@@ -2269,11 +2164,6 @@
           <t>পূর্বের মিউয়ন কণার নিজস্ব প্রসঙ্গ কাঠামোতে (Rest frame of muon) ব্যাখ্যা করো কীভাবে এটি ক্ষয় হওয়ার পূর্বেই ভূপৃষ্ঠ স্পর্শ করতে পারে।</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>মিউয়নের নিজস্ব কাঠামোতে মিউয়ন স্থির এবং এর জীবনকাল অপরিবর্তিত $\tau_0 = 2.2\ \mu\text{s}$। কিন্তু তার সাপেক্ষে বায়ুমণ্ডল $0.998c$ বেগে উপরের দিকে ধাবিত হচ্ছে। ফলে দৈর্ঘ্য সংকোচনের দরুন বায়ুমণ্ডলের $10\text{ km}$ উচ্চতা সংকুচিত হয়ে দাঁড়ায় $L = \frac{L_0}{\gamma} = \frac{10\text{ km}}{15.8} \approx 0.633\text{ km} = 633\text{ m}$। $2.2\ \mu\text{s}$ সময়ে বায়ুমণ্ডল অতিক্রম করে $0.998c \times 2.2\ \mu\text{s} \approx 658\text{ m} &gt; 633\text{ m}$। অর্থাৎ দৈর্ঘ্য সংকোচনের কারণে ভূপৃষ্ঠ তার কাছে এগিয়ে আসে।</t>
@@ -2319,11 +2209,6 @@
           <t>যমজ ভাইদের একজন রকেটে চড়ে তীব্র বেগে মহাকাশ ঘুরে ফিরে এলে অপর ভাই অপেক্ষা বয়সে তরুণ থাকে কেন? উভয় ভাইয়ের দৃষ্টিভঙ্গি কি সমানভাবে আপেক্ষিক?</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>উভয় দৃষ্টিভঙ্গি প্রতিসম নয়, কারণ পৃথিবীতে থাকা ভাই সর্বদা একটি জড় প্রসঙ্গ কাঠামোতে থাকে, কিন্তু রকেটের ভাইকে যাত্রা শুরু, দিক পরিবর্তন (ইউ-টার্ন) এবং অবতরণের সময় ত্বরণ ও মন্দন সহ্য করতে হয়। ত্বরণশীল হওয়ার কারণে রকেটের কাঠামো একটি অজড় কাঠামো। সাধারণ আপেক্ষিকতা ও স্থান-কালের ওয়ার্ল্ডলাইন বিশ্লেষণে দেখা যায় রকেটচারী ভাইয়ের স্পেসটাইম ট্র্যাজেক্টোরির প্রপার টাইম পৃথিবীর ভাই অপেক্ষা কম হয়। ফলে রকেটচারী ভাই-ই প্রকৃত অর্থে তরুণ থাকবে; কোনো আপাত অসঙ্গতি থাকে না।</t>
@@ -2369,11 +2254,6 @@
           <t>একটি চলন্ত ঘড়ি একটি স্থির ঘড়ির তুলনায় $60\%$ ধীরগতিতে চলতে থাকলে (অর্থাৎ স্থির ঘড়িতে ১ ঘণ্টা অতিক্রান্ত হলে চলন্ত ঘড়িতে $2.5$ ঘণ্টা নির্দেশিত হলে) ঘড়িটির বেগ আলোর বেগের কত শতাংশ?</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>সময় দীর্ঘায়ন: $t = \gamma t_0 \Rightarrow \gamma = \frac{t}{t_0} = 2.5 = \frac{5}{2}$। লরেন্টজ ফ্যাক্টর $\frac{1}{\sqrt{1 - \beta^2}} = \frac{5}{2} \Rightarrow \sqrt{1 - \beta^2} = \frac{2}{5} = 0.4$। বর্গ করলে: $1 - \beta^2 = 0.16 \Rightarrow \beta^2 = 0.84 \Rightarrow \beta = \sqrt{0.84} \approx 0.9165$। সুতরাং ঘড়িটির বেগ আলোর বেগের প্রায় $91.65\%$ ($v \approx 0.9165c$)।</t>
@@ -2419,11 +2299,6 @@
           <t>জিপিএস উপগ্রহগুলোতে পারমাণবিক ঘড়িগুলোর নিখুঁত সময় গণনায় বিশেষ আপেক্ষিকতার কাল দীর্ঘায়ন এবং সাধারণ আপেক্ষিকতার মহাকর্ষীয় কাল দীর্ঘায়ন কীভাবে পরস্পরবিরোধী ভূমিকা পালন করে?</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>বিশেষ আপেক্ষিকতা অনুযায়ী উপগ্রহের কক্ষীয় গতির ($v \approx 3.9\text{ km/s}$) জন্য ঘড়িটি প্রতিদিন প্রায় ৭ মাইক্রোসেকেন্ড ধীর হয় ($-7\ \mu\text{s/day}$)। অপরদিকে সাধারণ আপেক্ষিকতা অনুযায়ী উপগ্রহটি দুর্বল মহাকর্ষীয় বিভবে (ভূপৃষ্ঠ থেকে ২০,০০০ কিমি উঁচুতে) থাকায় মহাকর্ষীয় সময় প্রসারণের ফলে ঘড়িটি প্রতিদিন প্রায় ৪৫ মাইক্রোসেকেন্ড দ্রুত চলে ($+45\ \mu\text{s/day}$)। নেট ফলাফল হলো উপগ্রহের ঘড়ি প্রতিদিন প্রায় ৩৮ মাইক্রোসেকেন্ড দ্রুত চলে ($+38\ \mu\text{s/day}$), যা সংশোধন না করলে জিপিএস প্রতিদিন প্রায় ১১ কিমি অবস্থানের ত্রুটি দেখাত।</t>
@@ -2469,11 +2344,6 @@
           <t>একটি সুপারসনিক জেট বিমান $v = 600\text{ m/s}$ বেগে ১ দিন উড়লে স্থির পর্যবেক্ষকের তুলনায় এর ঘড়িতে কত সময়ের ব্যবধান সৃষ্টি হবে? ($c = 3 \times 10^8\text{ m/s}$)</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>যেহেতু $v \ll c$, দ্বিপদী বিস্তার অনুযায়ী $\gamma = (1 - v^2/c^2)^{-1/2} \approx 1 + \frac{v^2}{2c^2}$। সময় ব্যবধান $\Delta t - \Delta t_0 = \Delta t_0 (\gamma - 1) \approx \Delta t_0 \frac{v^2}{2c^2}$। এখানে $\Delta t_0 = 1\text{ দিন} = 86400\text{ s}$। $\frac{v^2}{2c^2} = \frac{(600)^2}{2 \times (3 \times 10^8)^2} = \frac{3.6 \times 10^5}{1.8 \times 10^{17}} = 2 \times 10^{-12}$। সুতরাং $\Delta t - \Delta t_0 = 86400 \times 2 \times 10^{-12} \approx 1.728 \times 10^{-7}\text{ s} \approx 0.173\ \mu\text{s}$।</t>
@@ -2519,11 +2389,6 @@
           <t>একটি ফোটন যদি সচেতন হতো, তবে তার নিজের সাপেক্ষে মহাবিশ্বের সৃষ্টি থেকে বর্তমান মুহূর্ত পর্যন্ত তার অতিক্রান্ত নিজস্ব সময় (Proper time) কত হতো?</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>ফোটন আলোর বেগে ($v = c$) চলে। ফোটনের জন্য স্থান-কাল ব্যবধান $ds^2 = c^2 d\tau^2 = c^2 dt^2 - dx^2 = 0$ (নাল জিওডেসিক)। এর ফলে ফোটনের সঠিক সময় ব্যবধান $d\tau = dt \sqrt{1 - v^2/c^2} = dt \sqrt{1 - 1} = 0$। অর্থাৎ আলোর বেগে গতিশীল কোনো কণার নিজস্ব সময়প্রবাহ সম্পূর্ণ স্তব্ধ হয়ে যায়। ফোটনের নিজস্ব সময়ানুযায়ী তার নিঃসরণ এবং শোষণ সম্পূর্ণ তাৎক্ষণিক (শূন্য সময় ব্যবধান)।</t>
@@ -2569,11 +2434,6 @@
           <t>১৯৭১ সালের হাফেল-কিটিং (Hafele-Keating) পরীক্ষায় সিজিয়াম পারমাণবিক ঘড়ি বিমানে করে পূর্ব ও পশ্চিম দিকে ঘুরিয়ে এনে ভূপৃষ্ঠের ঘড়ির সাথে তুলনা করে কী প্রমাণিত হয়েছিল?</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>হাফেল ও কিটিং বাণিজ্যিক বিমানে পারমাণবিক ঘড়ি নিয়ে পৃথিবীকে পূর্ব ও পশ্চিম দিকে প্রদক্ষিণ করেন। পৃথিবীর ঘূর্ণনের কারণে পূর্বগামী বিমানের গতি পৃথিবীর ঘূর্ণন বেগের সাথে যোগ হয় এবং পশ্চিমগামী বিমানের ক্ষেত্রে বিয়োগ হয়। বিশেষ আপেক্ষিকতার গতিজনিত সময় প্রসারণ এবং সাধারণ আপেক্ষিকতার মহাকর্ষীয় প্রসারণের যৌথ তাত্ত্বিক হিসাবের সাথে বাস্তব পারমাণবিক ঘড়ির ন্যানোসেকেন্ড স্তরের সময়ের অমিল নিখুঁতভাবে মিলে যায়, যা কাল দীর্ঘায়নের সরাসরি পরীক্ষামূলক প্রমাণ দেয়।</t>
@@ -2619,11 +2479,6 @@
           <t>একটি তেজস্ক্রিয় কণার অর্ধায়ু স্থির অবস্থায় $T_0$। কণাটির অর্ধায়ু পরিমাপ করে $2 T_0$ পাওয়া গেলে ল্যাবরেটরিতে কণাটির দ্রুতি আলোর দ্রুতির কত গুণ?</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>সময় দীর্ঘায়ন সূত্রানুযায়ী: $T = \gamma T_0 = 2 T_0 \Rightarrow \gamma = 2$। অতএব $\frac{1}{\sqrt{1 - \beta^2}} = 2 \Rightarrow 1 - \beta^2 = \frac{1}{4} = 0.25$। $\beta^2 = 1 - 0.25 = 0.75 \Rightarrow \beta = \sqrt{\frac{3}{4}} = \frac{\sqrt{3}}{2} \approx 0.866$। সুতরাং কণাটির দ্রুতি $v = \frac{\sqrt{3}}{2}c \approx 0.866c$।</t>
@@ -2669,11 +2524,6 @@
           <t>সঠিক দৈর্ঘ্য (Proper length) $L_0$ বলতে কী বোঝায়? গতির অভিমুখে একটি দণ্ডের দৈর্ঘ্য সংকোচনের সমীকরণটি লেখো এবং গতিশীল অবস্থায় গতির লম্ব দিকের দৈর্ঘ্যের কী পরিবর্তন ঘটে?</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>সঠিক দৈর্ঘ্য ($L_0$) হলো সেই দৈর্ঘ্য যা দণ্ডটির নিজস্ব নিশ্চল কাঠামোতে (যেখানে দণ্ডটি স্থির) পরিমাপ করা হয়। গতির অভিমুখে গতিশীল পর্যবেক্ষকের নিকট পরিমাপকৃত দৈর্ঘ্য $L = L_0 \sqrt{1 - \frac{v^2}{c^2}} = \frac{L_0}{\gamma}$। যেহেতু $\gamma &gt; 1$, তাই $L &lt; L_0$ হয়। তবে গতির সাথে লম্ব দিকের মাত্রার (যেমন প্রস্থ বা উচ্চতা) কোনো পরিবর্তন ঘটে না ($y' = y, z' = z$); কেবল গতির সমান্তরাল দিকেই সংকোচন ঘটে।</t>
@@ -2719,11 +2569,6 @@
           <t>স্থির অবস্থায় $R$ ব্যাসার্ধের একটি নিখুঁত গোলক $X$-অক্ষ বরাবর $0.8c$ বেগে গতিশীল হলে গতিশীল কাঠামোর স্থির পর্যবেক্ষকের নিকট এর ত্রিমাত্রিক রূপ কেমন হবে এবং এর আয়তন নিশ্চল আয়তনের কত শতাংশ হবে?</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>গোলকের $Y$ ও $Z$ অক্ষ বরাবর ব্যাস অপরিবর্তিত থাকবে ($2R$), কিন্তু গতির অভিমুখে ($X$-অক্ষ বরাবর) ব্যাস সংকুচিত হয়ে হবে $2R' = 2R \sqrt{1 - 0.8^2} = 2R \sqrt{0.36} = 0.6(2R)$। ফলে গোলকটি একটি চ্যাপ্টা উপগোলকে (Oblate Spheroid) পরিণত হবে। আয়তন $V = \frac{4}{3}\pi R' R R = \frac{4}{3}\pi (0.6R) R^2 = 0.6 V_0$। অর্থাৎ এর আয়তন নিশ্চল আয়তন $V_0$-এর $60\%$ হবে ($40\%$ সংকোচন ঘটবে)।</t>
@@ -2769,11 +2614,6 @@
           <t>একটি $20\text{ m}$ দীর্ঘ মই বা পোলকে কি $10\text{ m}$ দীর্ঘ একটি খামারে (Barn) আপেক্ষিকীয় গতিতে প্রবেশ করিয়ে এক মুহূর্তের জন্য উভয় দরজা বন্ধ করে আটকে রাখা সম্ভব? এর আপেক্ষিকীয় সমাধান কী?</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>যদি পোলটি $\gamma \ge 2$ (অর্থাৎ $v \ge \frac{\sqrt{3}}{2}c$) বেগে চলে, তবে খামারের সাপেক্ষে পোলের দৈর্ঘ্য সংকুচিত হয়ে $L = \frac{20}{2} = 10\text{ m}$ হয়ে যায় এবং খামারের কাঠামোতে উভয় দরজা একসাথে বন্ধ করা সম্ভব। কিন্তু পোলের নিজস্ব কাঠামোতে খামারটি সংকুচিত হয়ে মাত্র $5\text{ m}$ হয়ে যায়! এই আপাত প্যারাডক্সের সমাধান হলো এককালিনতার আপেক্ষিকতা (Relativity of simultaneity)। খামারের কাঠামোতে দুটি দরজা বন্ধ হওয়া এককালীন হলেও পোলের কাঠামোতে সামনের দরজাটি পিছনের দরজার অনেক আগেই খুলে যায়, ফলে পোলটি কখনই খামারের ভেতরে আটকা পড়ে না।</t>
@@ -2819,11 +2659,6 @@
           <t>একটি বস্তু স্থির অবস্থায় ভর $m_0$ এবং আয়তন $V_0$, ফলে নিশ্চল ঘনত্ব $\rho_0 = m_0/V_0$। বস্তুটি $v$ বেগে গতিশীল হলে গতিশীল ঘনত্ব $\rho$-এর সাথে নিশ্চল ঘনত্বের সম্পর্ক কী দাঁড়ায়?</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>গতিশীল অবস্থায় বস্তুর আপেক্ষিকীয় ভর বৃদ্ধি পায়: $m = \gamma m_0$। অপরদিকে গতির অভিমুখে দৈর্ঘ্য সংকুচিত হওয়ায় আয়তন হ্রাস পায়: $V = \frac{V_0}{\gamma}$। সুতরাং গতিশীল অবস্থায় ঘনত্ব $\rho = \frac{m}{V} = \frac{\gamma m_0}{V_0 / \gamma} = \gamma^2 \frac{m_0}{V_0} = \gamma^2 \rho_0 = \frac{\rho_0}{1 - \frac{v^2}{c^2}}$। অর্থাৎ ঘনত্ব $\gamma^2$ গুণ বৃদ্ধি পায়।</t>
@@ -2869,11 +2704,6 @@
           <t>একটি দণ্ড তার নিশ্চল কাঠামোতে $X$-অক্ষের সাথে $\theta_0$ কোণে আনত এবং এর দৈর্ঘ্য $L_0$। দণ্ডটি $X$-অক্ষ বরাবর $v$ বেগে চললে পরিমাপকৃত আনতি কোণ $\theta$ এবং নিশ্চল কোণ $\theta_0$-এর সম্পর্ক কী?</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>নিশ্চল কাঠামোতে উপাদান: $x_0 = L_0 \cos\theta_0$, $y_0 = L_0 \sin\theta_0$। গতিশীল অবস্থায়: $x = \frac{x_0}{\gamma} = \frac{L_0 \cos\theta_0}{\gamma}$, এবং $y = y_0 = L_0 \sin\theta_0$ (যেহেতু লম্ব দিকে সংকোচন নেই)। অতএব গতিশীল কাঠামোতে কোণ: $\tan\theta = \frac{y}{x} = \frac{L_0 \sin\theta_0}{(L_0 \cos\theta_0)/\gamma} = \gamma \tan\theta_0$। যেহেতু $\gamma &gt; 1$, তাই $\tan\theta &gt; \tan\theta_0 \Rightarrow \theta &gt; \theta_0$ (দণ্ডটি খাড়া মনে হবে)।</t>
@@ -2919,11 +2749,6 @@
           <t>আপেক্ষিকীয় দৈর্ঘ্য সংকোচনে গতিশীল বস্তুর দৈর্ঘ্য হ্রাস পায়। এই সংকোচন কি বস্তুর মধ্যে কোনো অভ্যন্তরীণ স্থিতিস্থাপক চাপ (Stress) সৃষ্টি করে বা এর পরমাণুগুলোকে সংকুচিত করে?</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>না, দৈর্ঘ্য সংকোচন কোনো অভ্যন্তরীণ যান্ত্রিক চাপ বা বিকৃতি সৃষ্টি করে না। বস্তুর নিজস্ব কাঠামোতে বস্তুটি সম্পূর্ণ অপরিবর্তিত থাকে এবং সেখানে কোনো বল বা পীড়ন নেই। দৈর্ঘ্য সংকোচন হলো স্থান-কালের জ্যামিতিক ধর্মের প্রতিফলন এবং এটি মূলত গতিশীল বস্তুটির দুটি প্রান্তবিন্দু ভিন্ন ভিন্ন সময়ে পরিমাপ করার (পরিমাপের এককালিনতার) আপেক্ষিক ফলাফল।</t>
@@ -2969,11 +2794,6 @@
           <t>দুটি ঘটনার মধ্যে স্থান-কাল ব্যবধান $\Delta s^2 = c^2 \Delta t^2 - \Delta x^2$ হলে $\Delta s^2 &gt; 0$, $\Delta s^2 &lt; 0$, এবং $\Delta s^2 = 0$ এর ভৌত তাৎপর্য কী?</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>(১) $\Delta s^2 &gt; 0$ (টাইমলাইক - Timelike): ঘটনা দুটির মধ্যে কার্য-কারণ সম্পর্ক স্থাপন সম্ভব এবং এমন একটি প্রসঙ্গ কাঠামো আছে যেখানে তারা একই স্থানে ঘটে। (২) $\Delta s^2 &lt; 0$ (স্পেসলাইক - Spacelike): এদের মধ্যে আলোর চেয়ে দ্রুত না চললে কার্য-কারণ সম্পর্ক অসম্ভব এবং এমন একটি কাঠামো আছে যেখানে তারা একই সময়ে ঘটে। (৩) $\Delta s^2 = 0$ (লাইটলাইক বা নাল - Lightlike): ঘটনা দুটি আলোর গতিতে চলমান একটি সংকেত দ্বারা সংযুক্ত হতে পারে।</t>
@@ -3019,11 +2839,6 @@
           <t>তাত্ত্বিকভাবে দৈর্ঘ্য সংকোচন ঘটলেও কোনো হাই-স্পিড ক্যামেরা দিয়ে তীব্র বেগে চলমান কোনো বস্তুর তাৎক্ষণিক ছবি তুললে তা সংকুচিত না দেখিয়ে সামান্য আবর্তিত (Rotated) দেখায় কেন?</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>১৯৫৯ সালে জেমস টেরেল ও রজার পেনরোজ দেখান যে একটি ছবি তোলার সময় ক্যামেরার শাটার নির্দিষ্ট মুহূর্তে সেই সমস্ত ফোটন ধারণ করে যা একসাথে ক্যামেরায় পৌঁছায়। বস্তুর দূরবর্তী অংশ থেকে আসা ফোটনগুলো নিকটবর্তী অংশের চেয়ে আগে নির্গত হতে হয়। এই সময়ের পার্থক্যের কারণে দৈর্ঘ্য সংকোচন এবং আলোর ভ্রমণের সময়ের প্রভাব যুক্ত হয়ে বস্তুটি সংকুচিত হওয়ার পরিবর্তে যেন কিছুটা কোণে ঘুরে গেছে (Optical rotation) বলে মনে হয়।</t>
@@ -3069,11 +2884,6 @@
           <t>স্থির অবস্থায় ১ মিটার দৈর্ঘ্যের একটি স্কেলকে গতিশীল অবস্থায় পরিমাপ করে $0.5\text{ m}$ পাওয়া গেল। স্কেলটির দ্রুতি কত এবং এর লরেন্টজ ফ্যাক্টর $\gamma$ কত?</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>দৈর্ঘ্য সংকোচন সূত্র: $L = \frac{L_0}{\gamma} \Rightarrow \gamma = \frac{L_0}{L} = \frac{1.0\text{ m}}{0.5\text{ m}} = 2$। অতএব $\frac{1}{\sqrt{1 - \beta^2}} = 2 \Rightarrow 1 - \beta^2 = \frac{1}{4} = 0.25 \Rightarrow \beta^2 = 0.75$। দ্রুতি $v = \sqrt{0.75}c = \frac{\sqrt{3}}{2}c \approx 0.866c$।</t>
@@ -3119,11 +2929,6 @@
           <t>দুটি অভিন্ন মহাকাশযান একই ত্বরণে সামনের দিকে চলতে শুরু করল এবং তাদের মাঝে একটি পাতলা সুতা বাঁধা ছিল। গতিশীল অবস্থায় সুতাটি কি অক্ষত থাকবে নাকি ছিঁড়ে যাবে?</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>ভূপৃষ্ঠের জড় কাঠামো অনুযায়ী উভয় রকেটের বেগ ও সরণ সর্বদা সমান, তাই তাদের মধ্যকার দূরত্ব ধ্রুব থাকে ($d$ অপরিবর্তিত)। কিন্তু রকেটগুলোর গতি বৃদ্ধির সাথে সাথে সুতাটির স্বাভাবিক রিল্যাক্সড প্রপার দৈর্ঘ্য সংকুচিত হতে চায় ($L = L_0/\gamma$)। যেহেতু বাহ্যিক দূরত্ব স্থির রাখা হয়েছে, তাই সুতাটির ওপর বিপুল আপেক্ষিকীয় টান (Relativistic stress) সৃষ্টি হয় এবং একপর্যায়ে সুতাটি ছিঁড়ে যাবে। এটি প্রমাণ করে ত্বরণশীল ব্যবস্থায় দৈর্ঘ্য সংকোচন বাস্তব যান্ত্রিক টান সৃষ্টি করতে পারে।</t>
@@ -3169,11 +2974,6 @@
           <t>একটি কণার স্থির ভর (Rest mass) $m_0$ হলে $v$ বেগে গতিশীল অবস্থায় এর আপেক্ষিকীয় ভর $m$-এর সমীকরণটি কী এবং কোনো বস্তু কি কখনোই আলোর গতিতে পৌঁছাতে পারে না কেন?</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>আপেক্ষিকীয় ভরের সমীকরণ $m = \frac{m_0}{\sqrt{1 - \frac{v^2}{c^2}}} = \gamma m_0$। যখন কণার বেগ আলোর বেগ $c$-এর দিকে ধাবিত হয় ($v \to c$), তখন হর $\sqrt{1 - v^2/c^2} \to 0$, ফলে ভর $m \to \infty$ (অসীম) হয়ে যায়। অসীম ভরসম্পন্ন কোনো বস্তুকে আরও ত্বরান্বিত করতে অসীম পরিমাণের শক্তির প্রয়োজন যা বাস্তবে অর্জন করা অসম্ভব। তাই অশূন্য স্থির ভরের কোনো বস্তু কখনই আলোর বেগে পৌঁছাতে পারে না।</t>
@@ -3219,11 +3019,6 @@
           <t>আইনস্টাইনের আপেক্ষিকীয় ভর-শক্তি তুল্যতা সমীকরণটি কী এবং একটি গতিশীল কণার মোট শক্তি $E$, স্থির শক্তি $E_0$ এবং গতিশক্তি $K$-এর মধ্যকার সম্পর্ক কী?</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>আইনস্টাইনের সার্বজনীন ভর-শক্তি সমীকরণ $E = m c^2 = \gamma m_0 c^2$। কণার স্থির শক্তি $E_0 = m_0 c^2$। গতিশক্তি $K$ হলো মোট শক্তি থেকে স্থির শক্তির বিয়োগফল: $K = E - E_0 = m c^2 - m_0 c^2 = (\gamma - 1)m_0 c^2$। ক্লাসিক্যাল মেকানিক্সের $\frac{1}{2}m v^2$ কেবল $v \ll c$ এর ক্ষেত্রে এর প্রথম-ক্রমের আসন্ন মান।</t>
@@ -3269,11 +3064,6 @@
           <t>আপেক্ষিকীয় মোট শক্তি $E$, ভরবেগ $p$ এবং স্থির ভর $m_0$-এর মধ্যকার বিখ্যাত ইনভেরিয়েন্ট সম্পর্কটি প্রতিপাদন করো। শূন্য স্থির ভরের কণার জন্য এটি কেমন রূপ নেয়?</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>আমরা জানি $E = \gamma m_0 c^2$ এবং $p = \gamma m_0 v$। এদের বর্গের বিয়োগফল: $E^2 - p^2 c^2 = \gamma^2 m_0^2 c^4 - \gamma^2 m_0^2 v^2 c^2 = \gamma^2 m_0^2 c^4 \left(1 - \frac{v^2}{c^2}\right) = \frac{1}{1 - v^2/c^2} m_0^2 c^4 \left(1 - \frac{v^2}{c^2}\right) = m_0^2 c^4$। সুতরাং $E^2 = p^2 c^2 + m_0^2 c^4$। শূন্য স্থির ভরের কণার জন্য ($m_0 = 0$, যেমন ফোটন) সমীকরণটি দাঁড়ায় $E = p c$ বা $p = \frac{E}{c}$।</t>
@@ -3319,11 +3109,6 @@
           <t>একটি কণার গতিশক্তি তার স্থির শক্তির সমান ($K = E_0$) হলে কণাটির দ্রুতি আলোর দ্রুতির কত গুণ হবে?</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>শর্তানুযায়ী $K = E_0 \Rightarrow E - E_0 = E_0 \Rightarrow E = 2 E_0$। যেহেতু $E = \gamma E_0$, সুতরাং $\gamma = 2$। লরেন্টজ ফ্যাক্টর $\frac{1}{\sqrt{1 - \beta^2}} = 2 \Rightarrow 1 - \beta^2 = \frac{1}{4} = 0.25 \Rightarrow \beta^2 = 0.75$। অতএব দ্রুতি $\beta = \sqrt{0.75} = \frac{\sqrt{3}}{2} \approx 0.866$। অর্থাৎ দ্রুতি হবে $v = \frac{\sqrt{3}}{2}c \approx 0.866c$।</t>
@@ -3369,11 +3154,6 @@
           <t>দ্বিপদী উপপাদ্য ব্যবহার করে দেখাও যে যখন $v \ll c$, তখন আপেক্ষিকীয় গতিশক্তি $K = (\gamma - 1)m_0 c^2$ হুবহু ক্লাসিক্যাল গতিশক্তি $\frac{1}{2}m_0 v^2$-এ পরিণত হয়।</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>লরেন্টজ ফ্যাক্টর $\gamma = \left(1 - \frac{v^2}{c^2}\right)^{-1/2}$। দ্বিপদী বিস্তার করলে: $\gamma = 1 + \frac{1}{2}\frac{v^2}{c^2} + \frac{3}{8}\frac{v^4}{c^4} + \dots$। গতিশক্তির রাশিতে বসালে: $K = (\gamma - 1)m_0 c^2 = \left(\frac{1}{2}\frac{v^2}{c^2} + \frac{3}{8}\frac{v^4}{c^4} + \dots\right) m_0 c^2 = \frac{1}{2}m_0 v^2 + \frac{3}{8}\frac{m_0 v^4}{c^2} + \dots$। যখন $v \ll c$, উচ্চ ঘাতযুক্ত পদগুলো শূন্যের কোঠায় পৌঁছায়, ফলে প্রথম পদটি থাকে: $K \approx \frac{1}{2}m_0 v^2$।</t>
@@ -3419,11 +3199,6 @@
           <t>একটি আপেক্ষিকীয় কণার গতিশক্তি $K$ এবং স্থির শক্তি $E_0 = m_0 c^2$ হলে কণাটির ভরবেগ $p$-এর সমীকরণটি $K$ এবং $E_0$-এর মাধ্যমে প্রকাশ করো।</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>আমরা জানি $E = K + E_0$। সূত্র: $E^2 = p^2 c^2 + E_0^2 \Rightarrow p^2 c^2 = E^2 - E_0^2 = (K + E_0)^2 - E_0^2 = K^2 + 2 K E_0 + E_0^2 - E_0^2 = K(K + 2E_0)$। অতএব ভরবেগ $p = \frac{\sqrt{K(K + 2E_0)}}{c} = \frac{\sqrt{K^2 + 2K m_0 c^2}}{c}$। (যদি $K \ll E_0$ হয় তবে $p \approx \frac{\sqrt{2K m_0 c^2}}{c} = \sqrt{2m_0 K}$, যা ক্লাসিক্যাল সূত্র)।</t>
@@ -3469,11 +3244,6 @@
           <t>আইনস্টাইনের সূত্রানুযায়ী $1.0\text{ g}$ ভর সম্পূর্ণরূপে শক্তিতে রূপান্তরিত হলে কত জুল শক্তি উৎপন্ন হবে এবং এই শক্তি কত মেগাওয়াট-ঘণ্টা (MWh) বিদ্যুতের সমতুল্য?</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>ভর $m = 1.0\text{ g} = 1.0 \times 10^{-3}\text{ kg}$। শক্তি $E = m c^2 = 1.0 \times 10^{-3}\text{ kg} \times (3 \times 10^8\text{ m/s})^2 = 1.0 \times 10^{-3} \times 9 \times 10^{16} = 9.0 \times 10^{13}\text{ J}$। মেগাওয়াট-ঘণ্টায় রূপান্তর: $1\text{ MWh} = 10^6\text{ W} \times 3600\text{ s} = 3.6 \times 10^9\text{ J}$। অতএব শক্তি $= \frac{9.0 \times 10^{13}}{3.6 \times 10^9} = 2.5 \times 10^4\text{ MWh} = 25,000\text{ MWh}$।</t>
@@ -3519,11 +3289,6 @@
           <t>একটি স্থির ইলেকট্রন এবং একটি স্থির পজিট্রন পরস্পর ধ্বংস হয়ে দুটি সমান শক্তির গামা ফোটন তৈরি করলে প্রতিটি ফোটনের ন্যূনতম শক্তি এবং কম্পাঙ্ক কত হবে? ($m_e = 9.1 \times 10^{-31}\text{ kg}$)</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>উভয় কণার মোট স্থির ভর $2 m_e$। উৎপন্ন শক্তি $E_{\text{total}} = 2 m_e c^2$। ভরবেগ সংরক্ষণের জন্য বিপরীতমুখী দুটি সমান ফোটন তৈরি হয়, তাই প্রতিটি ফোটনের শক্তি $E_{\gamma} = m_e c^2 = 9.1 \times 10^{-31}\text{ kg} \times (3 \times 10^8)^2\text{ J} = 8.19 \times 10^{-14}\text{ J}$। ইলেকট্রন ভোল্টে: $E_{\gamma} = \frac{8.19 \times 10^{-14}}{1.6 \times 10^{-19}}\text{ eV} \approx 0.511\text{ MeV}$। কম্পাঙ্ক $\nu = \frac{E}{h} = \frac{8.19 \times 10^{-14}\text{ J}}{6.626 \times 10^{-34}\text{ J}\cdot\text{s}} \approx 1.236 \times 10^{20}\text{ Hz}$।</t>
@@ -3569,11 +3334,6 @@
           <t>লার্জ হ্যাড্রন কোলাইডারে একটি প্রোটনের বেগ আলোর বেগের $99\%$ ($v = 0.99c$) হলে এর আপেক্ষিকীয় ভর স্থির ভরের কত গুণ হবে এবং এর মোট শক্তি স্থির শক্তির কত গুণ?</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>লরেন্টজ ফ্যাক্টর $\gamma = \frac{1}{\sqrt{1 - 0.99^2}} = \frac{1}{\sqrt{1 - 0.9801}} = \frac{1}{\sqrt{0.0199}} \approx \frac{1}{0.141} \approx 7.089$। আপেক্ষিকীয় ভর $m = \gamma m_0 \approx 7.09 m_0$। মোট শক্তি $E = m c^2 = \gamma E_0 \approx 7.09 E_0$। অর্থাৎ ভর এবং মোট শক্তি উভয়ই স্থির মানের প্রায় ৭.০৯ গুণ হবে।</t>
@@ -3619,11 +3379,6 @@
           <t>ফোটনের স্থির ভর শূন্য ($m_0 = 0$) হওয়া সত্ত্বেও এর ভরবেগ $p = \frac{h\nu}{c}$ থাকার রহস্য আপেক্ষিকীয় বলবিজ্ঞানের কোন তত্ত্ব দ্বারা ব্যাখ্যা করা যায়?</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I51" t="inlineStr">
         <is>
           <t>আপেক্ষিকীয় শক্তিসূত্র $E^2 = p^2 c^2 + m_0^2 c^4$। ফোটনের ক্ষেত্রে $m_0 = 0$ বসালে সরাসরি পাওয়া যায় $E^2 = p^2 c^2 \Rightarrow p = \frac{E}{c}$। প্ল্যাঙ্কের কোয়ান্টাম সমীকরণ অনুযায়ী ফোটনের শক্তি $E = h\nu$। ফলে ফোটনের গতিশীল ভরবেগ দাঁড়ায় $p = \frac{h\nu}{c} = \frac{h}{\lambda}$। ফোটন কখনই স্থির থাকতে পারে না, শূন্য মাধ্যমে সর্বদা $c$ বেগে চলে বলেই স্থির ভর শূন্য হলেও এর সসীম শক্তি ও ভরবেগ বজায় থাকে।</t>
@@ -3653,7 +3408,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>কাল দীর্ঘায়ন ও রকেটের গতিশীল ঘড়ি (সমস্যা 1)</t>
+          <t>আপেক্ষিকতার বিশেষ তত্ত্ব: কাল দীর্ঘায়ন, দৈর্ঘ্য সংকোচন ও ভর-শক্তি (Special Relativity)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3662,29 +3417,29 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>[সমস্যা 1: কাল দীর্ঘায়ন ও রকেটের গতিশীল ঘড়ি]
-একটি মহাশূন্যযান ভূমির সাপেক্ষে $v = 0.7c$ বেগে গতিশীল। নভোচারীর ঘড়িতে ১ বছর সময় অতিবাহিত হলে পৃথিবীতে থাকা সহকর্মীদের ঘড়িতে কত বছর সময় পার হবে?</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি মহাকাশযান পৃথিবীর সাপেক্ষে $v = 0.80 c$ বেগে ধাবমান। মহাকাশযানের ভেতরের একটি ঘড়িতে $1.0\text{ ঘণ্টা}$ অতিক্রান্ত হলে পৃথিবীর কোনো পর্যবেক্ষকের ঘড়িতে কত ঘণ্টা অতিক্রান্ত হবে?</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 1)।</t>
+          <t>লরেন্টজ গুণক $\gamma = \frac{1}{\sqrt{1 - v^2/c^2}} = \frac{1}{\sqrt{1 - 0.8^2}} = \frac{1}{\sqrt{1 - 0.64}} = \frac{1}{\sqrt{0.36}} = \frac{1}{0.60} = \frac{5}{3} \approx 1.6667$। কাল দীর্ঘায়ন সূত্র: $t = \gamma t_0 = \frac{5}{3} \times 1.0\text{ hr} = 1.667\text{ hr} = 1\text{ ঘণ্টা } 40\text{ মিনিট}$।</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>পৃথিবীর সময় $t = 1.667\text{ ঘণ্টা} = 1\text{ ঘণ্টা } 40\text{ মিনিট}$</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3704,12 +3459,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>দৈর্ঘ্য সংকোচন ও গতিশীল রড (সমস্যা 2)</t>
+          <t>আপেক্ষিকতার বিশেষ তত্ত্ব: কাল দীর্ঘায়ন, দৈর্ঘ্য সংকোচন ও ভর-শক্তি (Special Relativity)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -3717,25 +3472,25 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>[সমস্যা 2: দৈর্ঘ্য সংকোচন ও গতিশীল রড]
-স্থির অবস্থায় $L_0 = 100\text{ m}$ দীর্ঘ একটি ট্রেন $v = 0.8c$ বেগে প্ল্যাটফর্ম অতিক্রম করছে। প্ল্যাটফর্মের একজন স্থির দর্শকের কাছে ট্রেনের আপাত দৈর্ঘ্য কত মিটার মনে হবে?</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>##GEO:rect[w=5,h=2][size:small]##
+একটি রকেটের স্থির দৈর্ঘ্য (Proper length) $L_0 = 100.0\text{ m}$। রকেটটি কত বেগে গতিশীল হলে স্থির পর্যবেক্ষকের নিকট এর দৈর্ঘ্য সংকুচিত হয়ে $60.0\text{ m}$ মনে হবে?</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=5,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 2)।</t>
+          <t>দৈর্ঘ্য সংকোচন সূত্র: $L = L_0 \sqrt{1 - v^2/c^2} \implies 60.0 = 100.0 \sqrt{1 - v^2/c^2} \implies \sqrt{1 - v^2/c^2} = 0.60$। বর্গ করে: $1 - \frac{v^2}{c^2} = 0.36 \implies \frac{v^2}{c^2} = 0.64 \implies v = 0.80 c = 0.80 \times 3.0 \times 10^8 = 2.40 \times 10^8\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 2</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>রকেটের বেগ $v = 0.80 c = 2.40 \times 10^8\text{ m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3755,7 +3510,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>আপেক্ষিক ভর ও ভর-শক্তি সমতুল্যতা (সমস্যা 3)</t>
+          <t>আপেক্ষিকতার বিশেষ তত্ত্ব: কাল দীর্ঘায়ন, দৈর্ঘ্য সংকোচন ও ভর-শক্তি (Special Relativity)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3764,29 +3519,29 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>[সমস্যা 3: আপেক্ষিক ভর ও ভর-শক্তি সমতুল্যতা]
-একটি কণার গতিশীল ভর এর নিশ্চল ভরের 9 গুণ ($m = 9m_0$)। কণাটির গতিবেগ কত এবং এর মোট আপেক্ষিক শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি মিউয়ন কণার গড় আয়ুষ্কাল তার নিজস্ব কাঠামোতে (Proper lifetime) $\tau_0 = 2.2 \times 10^{-6}\text{ s}$। বায়ুমণ্ডলের উপরিভাগে সৃষ্টি হয়ে কণাটি $v = 0.995 c$ দ্রুতিতে ভূ-পৃষ্ঠের দিকে ধাবিত হলে: (ক) পৃথিবীর সাপেক্ষে এর কার্যকর আয়ুষ্কাল $\tau$ এবং (খ) ক্ষয়প্রাপ্ত হওয়ার পূর্বে এটি পৃথিবীতে কত কিলোমিটার দূরত্ব অতিক্রম করবে?</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 3)।</t>
+          <t>$\gamma = \frac{1}{\sqrt{1 - (0.995)^2}} = \frac{1}{\sqrt{1 - 0.990025}} = \frac{1}{\sqrt{0.009975}} \approx \frac{1}{0.09987} \approx 10.013$। (ক) পৃথিবীর সাপেক্ষে আয়ুষ্কাল $\tau = \gamma \tau_0 = 10.013 \times (2.2 \times 10^{-6}\text{ s}) \approx 2.203 \times 10^{-5}\text{ s}$। (খ) অতিক্রান্ত দূরত্ব $d = v \tau = (0.995 \times 3.0 \times 10^8\text{ m/s}) \times (2.203 \times 10^{-5}\text{ s}) \approx 2.985 \times 10^8 \times 2.203 \times 10^{-5} \approx 6576\text{ m} \approx 6.576\text{ km}$।</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 3</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>(ক) কার্যকর আয়ুষ্কাল $\tau = 2.20 \times 10^{-5}\text{ s}$, (খ) অতিক্রান্ত দূরত্ব $d = 6.57\text{ km}$</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3806,12 +3561,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>আলোকতড়িৎ ক্রিয়া ও নিবৃত্তি বিভব (সমস্যা 4)</t>
+          <t>আপেক্ষিকতার বিশেষ তত্ত্ব: কাল দীর্ঘায়ন, দৈর্ঘ্য সংকোচন ও ভর-শক্তি (Special Relativity)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -3819,31 +3574,25 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>##PRESET:photoelectric-setup[size:medium]##
-[সমস্যা 4: আলোকতড়িৎ ক্রিয়া ও নিবৃত্তি বিভব]
-##PRESET:photoelectric-setup[size:medium]##
-একটি ধাতব পৃষ্ঠের কার্য অপেক্ষক $W_0 = 6.2\text{ eV}$। ধাতুটির ওপর $\lambda = 2000\text{ \AA}$ তরঙ্গদৈর্ঘ্যের অতিবেগুনি রশ্মি আপতিত হলে নিঃসৃত ফোটো-ইলেকট্রনের সর্বোচ্চ গতিশক্তি ও নিবৃত্তি বিভব ($V_0$) কত?</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি বর্গাকার সমতল প্লেটের স্থির অবস্থায় প্রতি বাহু $a_0 = 1.0\text{ m}$। প্লেটটি তার একটি বাহুর সমান্তরালে $v = 0.60 c$ বেগে ধাবিত হলে গতিশীল অবস্থায় এর ক্ষেত্রফল কত হবে?</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>##PRESET:photoelectric-setup[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 4)।</t>
+          <t>গতির সমান্তরাল বাহুটি সংকুচিত হবে: $a = a_0 \sqrt{1 - 0.6^2} = 1.0 \times 0.80 = 0.80\text{ m}$। কিন্তু গতির লম্ব দিকের বাহু অপরিবর্তিত থাকবে: $b = a_0 = 1.0\text{ m}$। ফলে ক্ষেত্রফল $A = a \times b = 0.80 \times 1.0 = 0.80\text{ m}^2$।</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 4</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>সংকুচিত ক্ষেত্রফল $A = 0.80\text{ m}^2$</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3863,7 +3612,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ডি-ব্রগলী তরঙ্গদৈর্ঘ্য ও ইলেকট্রনের বেগ (সমস্যা 5)</t>
+          <t>আপেক্ষিকতার বিশেষ তত্ত্ব: কাল দীর্ঘায়ন, দৈর্ঘ্য সংকোচন ও ভর-শক্তি (Special Relativity)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3872,29 +3621,29 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>[সমস্যা 5: ডি-ব্রগলী তরঙ্গদৈর্ঘ্য ও ইলেকট্রনের বেগ]
-একটি ইলেকট্রনকে $V = 700\text{ V}$ বিভব পার্থক্যের মধ্য দিয়ে ত্বরান্বিত করা হলো। ইলেকট্রনটির সাথে সংশ্লিষ্ট ডি-ব্রগলী তরঙ্গদৈর্ঘ্য ($\lambda = \frac{12.27}{\sqrt{V}}\text{ \AA}$) কত?</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি কণার গতিশীল ভর তার স্থির ভরের দ্বিগুণ ($m = 2 m_0$)। কণাটির বেগ আলোর বেগ $c$-এর শতকরা কত ভাগ?</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 5)।</t>
+          <t>ভর বৃদ্ধি সমীকরণ: $m = \frac{m_0}{\sqrt{1 - v^2/c^2}} = 2m_0 \implies \sqrt{1 - v^2/c^2} = \frac{1}{2}$। বর্গ করে: $1 - \frac{v^2}{c^2} = \frac{1}{4} \implies \frac{v^2}{c^2} = \frac{3}{4} \implies v = \frac{\sqrt{3}}{2} c \approx 0.8660 c$।</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 5</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>কণাটির বেগ $v = \frac{\sqrt{3}}{2} c \approx 0.866 c$ ($86.60\% c$)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3914,12 +3663,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>কম্পটন সরণ ও ফোটন বিচ্ছুরণ (সমস্যা 6)</t>
+          <t>আপেক্ষিকতার বিশেষ তত্ত্ব: কাল দীর্ঘায়ন, দৈর্ঘ্য সংকোচন ও ভর-শক্তি (Special Relativity)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -3927,25 +3676,27 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>[সমস্যা 6: কম্পটন সরণ ও ফোটন বিচ্ছুরণ]
-একটি এক্স-রে ফোটন একটি স্থির ইলেকট্রনের সাথে সংঘর্ষে লিপ্ত হয়ে $\theta = 80^\circ$ কোণে বিক্ষিপ্ত হলো। ফোটনটির তরঙ্গদৈর্ঘ্যের কম্পটন বৃদ্ধি $\Delta\lambda = \frac{h}{m_0 c}(1 - \cos\theta)$ কত আর্মস্ট্রং?</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি স্থির গোলকের ব্যাসার্ধ $R$ এবং ঘনত্ব $+ho_0$। গোলকটি $x$-অক্ষ বরাবর $v$ বেগে গতিশীল হলে এর আপেক্ষিক ঘনত্ব $+ho$ কত হবে?</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 6)।</t>
+          <t>ভর বৃদ্ধি পায়: $m = \gamma m_0$। দৈর্ঘ্য কেবল গতির অভিমুখে সংকুচিত হওয়ায় আয়তন সংকুচিত হয়: $V = V_0/\gamma$। অতএব ঘনত্ব $\rho = \frac{m}{V} = \frac{\gamma m_0}{V_0/\gamma} = \gamma^2 \frac{m_0}{V_0} = \gamma^2 \rho_0 = \frac{\rho_0}{1 - v^2/c^2}$।</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 6</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>আপেক্ষিক ঘনত্ব $\rho = \frac{\rho_0}{1 - v^2/c^2} = \gamma^2 \rho_0$</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3965,7 +3716,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>এক্স-রে নলের কাট-অফ তরঙ্গদৈর্ঘ্য (সমস্যা 7)</t>
+          <t>আপেক্ষিকতার বিশেষ তত্ত্ব: কাল দীর্ঘায়ন, দৈর্ঘ্য সংকোচন ও ভর-শক্তি (Special Relativity)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3974,29 +3725,29 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>[সমস্যা 7: এক্স-রে নলের কাট-অফ তরঙ্গদৈর্ঘ্য]
-একটি কুলিজ নলে $V = 90\text{ kV}$ বিভব প্রযুক্ত থাকলে উৎপন্ন এক্স-রের ন্যূনতম তরঙ্গদৈর্ঘ্য (Cut-off wavelength, $\lambda_{min} = \frac{hc}{eV}$) কত?</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+আইনস্টাইনের বেগ সংযোজন সূত্র: একটি মহাকাশযান পৃথিবীর সাপেক্ষে $u = 0.70 c$ বেগে চলছে। মহাকাশযানটি তার গতির অভিমুখে পৃথিবীর সাপেক্ষে $v' = 0.80 c$ বেগে একটি প্রোব নিক্ষেপ করল। পৃথিবীর পর্যবেক্ষকের সাপেক্ষে প্রোবটির বেগ $v$ কত?</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 7)।</t>
+          <t>আপেক্ষিক বেগ সংযোজন সূত্র: $v = \frac{u + v'}{1 + \frac{u v'}{c^2}} = \frac{0.70 c + 0.80 c}{1 + (0.70)(0.80)} = \frac{1.50 c}{1 + 0.56} = \frac{1.50}{1.56} c \approx 0.9615 c$ (আলোর বেগের চেয়ে কম থাকে)।</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 7</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>প্রোবের বেগ $v = 0.9615 c$</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4016,12 +3767,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>হাইজেনবার্গের অনিশ্চয়তা নীতি (সমস্যা 8)</t>
+          <t>আপেক্ষিকতার বিশেষ তত্ত্ব: কাল দীর্ঘায়ন, দৈর্ঘ্য সংকোচন ও ভর-শক্তি (Special Relativity)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -4029,25 +3780,25 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>[সমস্যা 8: হাইজেনবার্গের অনিশ্চয়তা নীতি]
-একটি গতিশীল ইলেকট্রনের অবস্থান পরিমাপে অনিশ্চয়তা $\Delta x = 0.6\text{ nm}$। হাইজেনবার্গের অনিশ্চয়তা নীতিানুসারে ইলেকট্রনটির ভরবেগ পরিমাপে ন্যূনতম অনিশ্চয়তা কত?</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি ইলেকট্রনের স্থির শক্তি $E_0 = m_0 c^2 = 0.511\text{ MeV}$। ইলেকট্রনটির গতিশক্তি $K = 1.022\text{ MeV}$ (স্থির শক্তির দ্বিগুণ) হলে ইলেকট্রনটির মোট শক্তি $E$ এবং বেগ $v$ কত?</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 8)।</t>
+          <t>মোট শক্তি $E = K + E_0 = 1.022 + 0.511 = 1.533\text{ MeV}$। আবার $E = \gamma E_0 \implies \gamma = \frac{1.533}{0.511} = 3.0$। $\gamma = \frac{1}{\sqrt{1 - v^2/c^2}} = 3 \implies 1 - \frac{v^2}{c^2} = \frac{1}{9} \implies \frac{v^2}{c^2} = \frac{8}{9} \implies v = \frac{\sqrt{8}}{3} c = \frac{2\sqrt{2}}{3} c \approx 0.9428 c$।</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 8</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>মোট শক্তি $E = 1.533\text{ MeV}$, বেগ $v = 0.943 c$</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4067,7 +3818,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ভর ত্রুটি হতে উৎপন্ন শক্তির পরিমাণ (সমস্যা 9)</t>
+          <t>আপেক্ষিকতার বিশেষ তত্ত্ব: কাল দীর্ঘায়ন, দৈর্ঘ্য সংকোচন ও ভর-শক্তি (Special Relativity)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4076,29 +3827,29 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>[সমস্যা 9: ভর ত্রুটি হতে উৎপন্ন শক্তির পরিমাণ]
-একটি পারমাণবিক ফিশন বিক্রিয়ায় $1\text{ g}$ ভর সম্পূর্ণরূপে শক্তিতে রূপান্তরিত হলে আইনস্টাইনের সমীকরণ $E = mc^2$ অনুযায়ী কত জুল বা কিলোওয়াট-ঘণ্টা শক্তি নির্গত হবে?</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি কণার ভরবেগ $p$ এবং মোট আপেক্ষিক শক্তি $E$-এর মধ্যকার সম্পর্ক $E^2 = p^2 c^2 + m_0^2 c^4$ প্রমাণ কর। ভরহীন কণার (যেমন ফোটন, $m_0 = 0$) ক্ষেত্রে ভরবেগ ও শক্তির সম্পর্ক কী?</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 9)।</t>
+          <t>$E = \gamma m_0 c^2$ এবং $p = \gamma m_0 v$। $E^2 - p^2 c^2 = \gamma^2 m_0^2 c^4 - \gamma^2 m_0^2 v^2 c^2 = \gamma^2 m_0^2 c^4\left(1 - \frac{v^2}{c^2}\right)$। যেহেতু $\gamma^2 = \frac{1}{1 - v^2/c^2}$, তাই পদটি কাটাকাটি গিয়ে থাকে $m_0^2 c^4$। অতএব $E^2 = p^2 c^2 + m_0^2 c^4$। $m_0 = 0$ হলে $E = p c$।</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 9</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>$E^2 = p^2 c^2 + m_0^2 c^4$, ফোটনের জন্য $E = p c \implies p = \frac{E}{c} = \frac{h}{\lambda}$</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4118,12 +3869,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>সূচনা কম্পাঙ্ক ও কার্য-অপেক্ষক (সমস্যা 10)</t>
+          <t>আপেক্ষিকতার বিশেষ তত্ত্ব: কাল দীর্ঘায়ন, দৈর্ঘ্য সংকোচন ও ভর-শক্তি (Special Relativity)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -4131,25 +3882,25 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>[সমস্যা 10: সূচনা কম্পাঙ্ক ও কার্য-অপেক্ষক]
-সিজিয়াম ধাতুর সূচনা তরঙ্গদৈর্ঘ্য $\lambda_0 = 8500\text{ \AA}$। ধাতুটির কার্য-অপেক্ষক ($W_0 = hc/\lambda_0$) ইলেকট্রন-ভোল্ট (eV) এককে নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+১ মিলিগ্রাম ($1.0\text{ mg}$) পদার্থ সম্পূর্ণরূপে শক্তিতে রূপান্তরিত হলে কত জুল শক্তি নির্গত হবে? এই শক্তিতে একটি $100\text{ W}$ বাতি কত বছর একটানা জ্বলতে পারবে?</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 10)।</t>
+          <t>ভর $m = 1.0 \times 10^{-6}\text{ kg}$। আইনস্টাইনের শক্তি সমীকরণ: $E = m c^2 = (1.0 \times 10^{-6}\text{ kg}) \times (3.0 \times 10^8\text{ m/s})^2 = 9.0 \times 10^{10}\text{ J}$। বাতির ক্ষমতা $P = 100\text{ W} = 100\text{ J/s}$। সময় $t = \frac{9.0 \times 10^{10}}{100} = 9.0 \times 10^8\text{ s}$। বছরে রূপান্তর: $t = \frac{9.0 \times 10^8}{365.25 \times 24 \times 3600} = \frac{9.0 \times 10^8}{3.1558 \times 10^7} \approx 28.52\text{ বছর}$।</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 10</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>মুক্ত শক্তি $E = 9.0 \times 10^{10}\text{ J}$, বাতিটি একটানা প্রায় $28.5$ বছর জ্বলবে</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4169,38 +3920,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>কাল দীর্ঘায়ন ও রকেটের গতিশীল ঘড়ি (সমস্যা 11)</t>
+          <t>আলোক তড়িৎ ক্রিয়া ও আইনস্টাইনের সমীকরণ (Photoelectric Effect)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>[সমস্যা 11: কাল দীর্ঘায়ন ও রকেটের গতিশীল ঘড়ি]
-একটি মহাশূন্যযান ভূমির সাপেক্ষে $v = 0.9c$ বেগে গতিশীল। নভোচারীর ঘড়িতে ১ বছর সময় অতিবাহিত হলে পৃথিবীতে থাকা সহকর্মীদের ঘড়িতে কত বছর সময় পার হবে?</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+একটি ধাতুর কার্য-অপেক্ষক (Work function) $W_0 = 2.40\text{ eV}$। ধাতুটির সূচনা কম্পাঙ্ক $f_0$ এবং সূচনা তরঙ্গদৈর্ঘ্য (Threshold wavelength $\lambda_0$) নির্ণয় কর। ($h = 6.626 \times 10^{-34}\text{ J}\cdot\text{s}, 1\text{ eV} = 1.6 \times 10^{-19}\text{ J}$)।</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 11)।</t>
+          <t>কার্য-অপেক্ষক $W_0 = 2.40 \times 1.6 \times 10^{-19}\text{ J} = 3.84 \times 10^{-19}\text{ J}$। সূচনা কম্পাঙ্ক $f_0 = \frac{W_0}{h} = \frac{3.84 \times 10^{-19}}{6.626 \times 10^{-34}} \approx 5.795 \times 10^{14}\text{ Hz}$। সূচনা তরঙ্গদৈর্ঘ্য $\lambda_0 = \frac{c}{f_0} = \frac{3.0 \times 10^8}{5.795 \times 10^{14}} \approx 5.1768 \times 10^{-7}\text{ m} = 517.7\text{ nm}$।</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 11</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>সূচনা কম্পাঙ্ক $f_0 = 5.79 \times 10^{14}\text{ Hz}$, সূচনা তরঙ্গদৈর্ঘ্য $\lambda_0 = 517.7\text{ nm} = 5177\text{ Å}$</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4220,7 +3971,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>দৈর্ঘ্য সংকোচন ও গতিশীল রড (সমস্যা 12)</t>
+          <t>আলোক তড়িৎ ক্রিয়া ও আইনস্টাইনের সমীকরণ (Photoelectric Effect)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4233,25 +3984,25 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>[সমস্যা 12: দৈর্ঘ্য সংকোচন ও গতিশীল রড]
-স্থির অবস্থায় $L_0 = 100\text{ m}$ দীর্ঘ একটি ট্রেন $v = 0.6c$ বেগে প্ল্যাটফর্ম অতিক্রম করছে। প্ল্যাটফর্মের একজন স্থির দর্শকের কাছে ট্রেনের আপাত দৈর্ঘ্য কত মিটার মনে হবে?</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি ধাতুর ওপর $\lambda = 300\text{ nm}$ অতিবেগুনী আলো আপতিত হওয়ায় নির্গত ইলেকট্রনগুলোর সর্বোচ্চ গতিশক্তি পাওয়া গেল $K_{\max} = 1.50\text{ eV}$। ধাতুটির কার্য-অপেক্ষক $W_0$ এবং নিবৃত্তি বিভব (Stopping potential $V_s$) কত?</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 12)।</t>
+          <t>ফোটনের শক্তি $E = \frac{h c}{\lambda} = \frac{1240\text{ eV}\cdot\text{nm}}{300\text{ nm}} \approx 4.133\text{ eV}$ (বা $\frac{6.626 \times 10^{-34} \times 3 \times 10^8}{300 \times 10^{-9} \times 1.6 \times 10^{-19}} = 4.141\text{ eV}$)। আইনস্টাইনের সমীকরণ: $E = W_0 + K_{\max} \implies W_0 = E - K_{\max} = 4.14 - 1.50 = 2.64\text{ eV}$। নিবৃত্তি বিভব $e V_s = K_{\max} = 1.50\text{ eV} \implies V_s = 1.50\text{ V}$।</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 12</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>কার্য-অপেক্ষক $W_0 = 2.64\text{ eV}$, নিবৃত্তি বিভব $V_s = 1.50\text{ V}$</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4271,38 +4022,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>আপেক্ষিক ভর ও ভর-শক্তি সমতুল্যতা (সমস্যা 13)</t>
+          <t>আলোক তড়িৎ ক্রিয়া ও আইনস্টাইনের সমীকরণ (Photoelectric Effect)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>[সমস্যা 13: আপেক্ষিক ভর ও ভর-শক্তি সমতুল্যতা]
-একটি কণার গতিশীল ভর এর নিশ্চল ভরের 7 গুণ ($m = 7m_0$)। কণাটির গতিবেগ কত এবং এর মোট আপেক্ষিক শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি ধাতব পাতে নির্দিষ্ট আলোর ক্ষেত্রে নিবৃত্তি বিভব $V_s = 2.0\text{ V}$। নির্গত ফটো-ইলেকট্রনের সর্বোচ্চ বেগ $v_{\max}$ কত কিমি/সেকেন্ড? ($m_e = 9.11 \times 10^{-31}\text{ kg}$)।</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 13)।</t>
+          <t>সর্বোচ্চ গতিশক্তি $K_{\max} = e V_s = (1.6 \times 10^{-19}\text{ C}) \times 2.0\text{ V} = 3.20 \times 10^{-19}\text{ J}$। $K_{\max} = \frac{1}{2}m_e v_{\max}^2 \implies v_{\max} = \sqrt{\frac{2 K_{\max}}{m_e}} = \sqrt{\frac{2(3.20 \times 10^{-19})}{9.11 \times 10^{-31}}} = \sqrt{\frac{6.40 \times 10^{-19}}{9.11 \times 10^{-31}}} = \sqrt{7.025 \times 10^{11}} \approx 8.3816 \times 10^5\text{ m/s} = 838.16\text{ km/s}$।</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 13</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>সর্বোচ্চ বেগ $v_{\max} = 8.38 \times 10^5\text{ m/s} = 838.0\text{ km/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4322,7 +4073,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>আলোকতড়িৎ ক্রিয়া ও নিবৃত্তি বিভব (সমস্যা 14)</t>
+          <t>আলোক তড়িৎ ক্রিয়া ও আইনস্টাইনের সমীকরণ (Photoelectric Effect)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4335,31 +4086,25 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>##PRESET:photoelectric-setup[size:medium]##
-[সমস্যা 14: আলোকতড়িৎ ক্রিয়া ও নিবৃত্তি বিভব]
-##PRESET:photoelectric-setup[size:medium]##
-একটি ধাতব পৃষ্ঠের কার্য অপেক্ষক $W_0 = 8.2\text{ eV}$। ধাতুটির ওপর $\lambda = 6000\text{ \AA}$ তরঙ্গদৈর্ঘ্যের অতিবেগুনি রশ্মি আপতিত হলে নিঃসৃত ফোটো-ইলেকট্রনের সর্বোচ্চ গতিশক্তি ও নিবৃত্তি বিভব ($V_0$) কত?</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি ধাতব পাতে আলোর কম্পাঙ্ক $f_1 = 8.0 \times 10^{14}\text{ Hz}$ হলে নিবৃত্তি বিভব হয় $1.20\text{ V}$ এবং কম্পাঙ্ক বাড়িয়ে $f_2 = 1.20 \times 10^{15}\text{ Hz}$ করলে নিবৃত্তি বিভব হয় $2.85\text{ V}$। এই উপাত্ত হতে প্ল্যাঙ্কের ধ্রুবক $h$ এবং ধাতুর সূচনা কম্পাঙ্ক $f_0$ নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>##PRESET:photoelectric-setup[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 14)।</t>
+          <t>আইনস্টাইনের সমীকরণ: $e V_s = h f - W_0 \implies e(V_{s2} - V_{s1}) = h(f_2 - f_1)$। $h = \frac{e(V_{s2} - V_{s1})}{f_2 - f_1} = \frac{(1.6 \times 10^{-19})(2.85 - 1.20)}{(1.20 - 0.80) \times 10^{15}} = \frac{1.6 \times 10^{-19} \times 1.65}{0.40 \times 10^{15}} = \frac{2.64 \times 10^{-19}}{4.0 \times 10^{14}} = 6.60 \times 10^{-34}\text{ J}\cdot\text{s}$। সূচনা কম্পাঙ্ক $W_0 = h f_1 - e V_{s1} = (6.60 \times 10^{-34})(8 \times 10^{14}) - (1.6 \times 10^{-19})(1.20) = 5.28 \times 10^{-19} - 1.92 \times 10^{-19} = 3.36 \times 10^{-19}\text{ J}$। $f_0 = \frac{W_0}{h} = \frac{3.36 \times 10^{-19}}{6.60 \times 10^{-34}} \approx 5.09 \times 10^{14}\text{ Hz}$।</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 14</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>$h = 6.60 \times 10^{-34}\text{ J}\cdot\text{s}, f_0 = 5.09 \times 10^{14}\text{ Hz}$</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4379,38 +4124,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ডি-ব্রগলী তরঙ্গদৈর্ঘ্য ও ইলেকট্রনের বেগ (সমস্যা 15)</t>
+          <t>আলোক তড়িৎ ক্রিয়া ও আইনস্টাইনের সমীকরণ (Photoelectric Effect)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>[সমস্যা 15: ডি-ব্রগলী তরঙ্গদৈর্ঘ্য ও ইলেকট্রনের বেগ]
-একটি ইলেকট্রনকে $V = 900\text{ V}$ বিভব পার্থক্যের মধ্য দিয়ে ত্বরান্বিত করা হলো। ইলেকট্রনটির সাথে সংশ্লিষ্ট ডি-ব্রগলী তরঙ্গদৈর্ঘ্য ($\lambda = \frac{12.27}{\sqrt{V}}\text{ \AA}$) কত?</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+আলোক তড়িৎ ক্রিয়ায় আপতিত আলোর তীব্রতা দ্বিগুণ করা হলে: (ক) ফটো-ইলেকট্রনের সর্বোচ্চ গতিশক্তি, (খ) নিবৃত্তি বিভব এবং (গ) ফটো তড়িৎ প্রবাহের (Saturation current) কী পরিবর্তন ঘটবে?</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 15)।</t>
+          <t>ফোটন তত্ত্বানুযায়ী আলোর তীব্রতা বৃদ্ধির অর্থ হলো প্রতি সেকেন্ডে আপতিত ফোটনের সংখ্যা বৃদ্ধি পাওয়া, কিন্তু প্রতিটি একক ফোটনের শক্তি $E = h f$ অপরিবর্তিত থাকে। ফলে নির্গত ইলেকট্রনের সর্বোচ্চ গতিশক্তি এবং নিবৃত্তি বিভব অপরিবর্তিত থাকে। কিন্তু প্রতি সেকেন্ডে নির্গত ইলেকট্রন সংখ্যা দ্বিগুণ হওয়ায় সম্পৃক্ত আলোক তড়িৎ প্রবাহ দ্বিগুণ বৃদ্ধি পায়।</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 15</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>(ক) গতিশক্তি অপরিবর্তিত থাকবে, (খ) নিবৃত্তি বিভব অপরিবর্তিত থাকবে, (গ) ফটো-কারেন্ট ঠিক দ্বিগুণ হবে</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4430,7 +4175,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>কম্পটন সরণ ও ফোটন বিচ্ছুরণ (সমস্যা 16)</t>
+          <t>আলোক তড়িৎ ক্রিয়া ও আইনস্টাইনের সমীকরণ (Photoelectric Effect)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4443,25 +4188,25 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>[সমস্যা 16: কম্পটন সরণ ও ফোটন বিচ্ছুরণ]
-একটি এক্স-রে ফোটন একটি স্থির ইলেকট্রনের সাথে সংঘর্ষে লিপ্ত হয়ে $\theta = 60^\circ$ কোণে বিক্ষিপ্ত হলো। ফোটনটির তরঙ্গদৈর্ঘ্যের কম্পটন বৃদ্ধি $\Delta\lambda = \frac{h}{m_0 c}(1 - \cos\theta)$ কত আর্মস্ট্রং?</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি $100\text{ W}$ ক্ষমতার সোডিয়াম বাতি হতে $\lambda = 589\text{ nm}$ হলুদ আলো চারদিকে সমভাবে বিকিরিত হচ্ছে। বাতিটি হতে প্রতি সেকেন্ডে কতটি ফোটন নিঃসৃত হয়?</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 16)।</t>
+          <t>একটি ফোটনের শক্তি $E_p = \frac{h c}{\lambda} = \frac{(6.626 \times 10^{-34}) \times (3.0 \times 10^8)}{589 \times 10^{-9}} = \frac{1.9878 \times 10^{-25}}{5.89 \times 10^{-7}} \approx 3.375 \times 10^{-19}\text{ J}$। প্রতি সেকেন্ডে মোট শক্তি $P = 100\text{ J}$। ফোটন সংখ্যা $N = \frac{P}{E_p} = \frac{100}{3.375 \times 10^{-19}} \approx 2.963 \times 10^{20}\text{ টি/সেকেন্ড}$।</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 16</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+          <t>ফোটন নিঃসরণের হার $N = 2.96 \times 10^{20}\text{ টি/সেকেন্ড}$</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4481,38 +4226,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>এক্স-রে নলের কাট-অফ তরঙ্গদৈর্ঘ্য (সমস্যা 17)</t>
+          <t>আলোক তড়িৎ ক্রিয়া ও আইনস্টাইনের সমীকরণ (Photoelectric Effect)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>[সমস্যা 17: এক্স-রে নলের কাট-অফ তরঙ্গদৈর্ঘ্য]
-একটি কুলিজ নলে $V = 70\text{ kV}$ বিভব প্রযুক্ত থাকলে উৎপন্ন এক্স-রের ন্যূনতম তরঙ্গদৈর্ঘ্য (Cut-off wavelength, $\lambda_{min} = \frac{hc}{eV}$) কত?</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি ধাতুর ওপর আপতিত আলোর তরঙ্গদৈর্ঘ্য $400\text{ nm}$ হতে কমিয়ে $300\text{ nm}$ করা হলে নিবৃত্তি বিভবের বৃদ্ধি $\Delta V_s$ কত ভোল্ট হবে?</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 17)।</t>
+          <t>নিবৃত্তি বিভব পরিবর্তন: $e \Delta V_s = h c\left(\frac{1}{\lambda_2} - \frac{1}{\lambda_1}\right)$। $\Delta V_s = \frac{h c}{e}\left(\frac{\lambda_1 - \lambda_2}{\lambda_1 \lambda_2}\right) = 1240\text{ V}\cdot\text{nm} \times \left(\frac{400 - 300}{400 \times 300}\right) = 1240 \times \frac{100}{120000} = \frac{1240}{1200} \approx 1.0333\text{ V}$।</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 17</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>নিবৃত্তি বিভবের বৃদ্ধি $\Delta V_s = 1.034\text{ V}$</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4532,7 +4277,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>হাইজেনবার্গের অনিশ্চয়তা নীতি (সমস্যা 18)</t>
+          <t>আলোক তড়িৎ ক্রিয়া ও আইনস্টাইনের সমীকরণ (Photoelectric Effect)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4545,25 +4290,25 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>[সমস্যা 18: হাইজেনবার্গের অনিশ্চয়তা নীতি]
-একটি গতিশীল ইলেকট্রনের অবস্থান পরিমাপে অনিশ্চয়তা $\Delta x = 0.8\text{ nm}$। হাইজেনবার্গের অনিশ্চয়তা নীতিানুসারে ইলেকট্রনটির ভরবেগ পরিমাপে ন্যূনতম অনিশ্চয়তা কত?</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি আলোক তড়িৎ কোষে ক্যাথোড হতে অ্যানোডে কোনো ইলেকট্রন পৌঁছাতে না পারার শর্তে নিবৃত্তি বিভব $V_s$। দেখাও যে নিবৃত্তি বিভব এবং কম্পাঙ্কের লেখচিত্রের ঢাল সার্বজনীন ধ্রুবক $rac{h}{e}$ নির্দেশ করে।</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 18)।</t>
+          <t>আইনস্টাইনের সমীকরণ: $e V_s = h f - W_0 \implies V_s = \left(\frac{h}{e}\right)f - \frac{W_0}{e}$। এটি $y = mx + c$ আকারের একটি সরলরেখা নির্দেশ করে যার ঢাল $m = \frac{h}{e}$। যেকোনো ধাতুর জন্যই এই ঢাল সর্বদা অপরিবর্তিত থাকে এবং $y$-অক্ষের ছেদিতাংশ $-\frac{W_0}{e}$ হতে ধাতুর কার্য-অপেক্ষক নির্ণয় করা যায়।</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 18</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>ঢাল $m = \frac{h}{e} \approx 4.14 \times 10^{-15}\text{ V}\cdot\text{s}$ (ধাতুর প্রকৃতির ওপর সম্পূর্ণ স্বাধীন)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4583,38 +4328,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ভর ত্রুটি হতে উৎপন্ন শক্তির পরিমাণ (সমস্যা 19)</t>
+          <t>আলোক তড়িৎ ক্রিয়া ও আইনস্টাইনের সমীকরণ (Photoelectric Effect)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>[সমস্যা 19: ভর ত্রুটি হতে উৎপন্ন শক্তির পরিমাণ]
-একটি পারমাণবিক ফিশন বিক্রিয়ায় $1\text{ g}$ ভর সম্পূর্ণরূপে শক্তিতে রূপান্তরিত হলে আইনস্টাইনের সমীকরণ $E = mc^2$ অনুযায়ী কত জুল বা কিলোওয়াট-ঘণ্টা শক্তি নির্গত হবে?</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি ফোটনের শক্তি $E = 1.0\text{ MeV}$। ফোটনটির সমতুল্য আপেক্ষিক ভর $m$ এবং রৈখিক ভরবেগ $p$ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 19)।</t>
+          <t>শক্তি $E = 1.0 \times 10^6 \times 1.6 \times 10^{-19}\text{ J} = 1.6 \times 10^{-13}\text{ J}$। সমতুল্য ভর $m = \frac{E}{c^2} = \frac{1.6 \times 10^{-13}}{(3.0 \times 10^8)^2} = \frac{1.6 \times 10^{-13}}{9.0 \times 10^{16}} \approx 1.778 \times 10^{-30}\text{ kg}$। ভরবেগ $p = \frac{E}{c} = \frac{1.6 \times 10^{-13}}{3.0 \times 10^8} \approx 5.333 \times 10^{-22}\text{ kg}\cdot\text{m/s}$।</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 19</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>সমতুল্য ভর $m = 1.78 \times 10^{-30}\text{ kg}$, ভরবেগ $p = 5.33 \times 10^{-22}\text{ kg}\cdot\text{m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4634,7 +4379,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>সূচনা কম্পাঙ্ক ও কার্য-অপেক্ষক (সমস্যা 20)</t>
+          <t>আলোক তড়িৎ ক্রিয়া ও আইনস্টাইনের সমীকরণ (Photoelectric Effect)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4647,25 +4392,25 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>[সমস্যা 20: সূচনা কম্পাঙ্ক ও কার্য-অপেক্ষক]
-সিজিয়াম ধাতুর সূচনা তরঙ্গদৈর্ঘ্য $\lambda_0 = 6500\text{ \AA}$। ধাতুটির কার্য-অপেক্ষক ($W_0 = hc/\lambda_0$) ইলেকট্রন-ভোল্ট (eV) এককে নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+চিরায়ত তরঙ্গ তত্ত্ব (Classical wave theory) কেন আলোক তড়িৎ ক্রিয়া ব্যাখ্যায় সম্পূর্ণ ব্যর্থ হয়েছিল? তিনটি প্রধান ব্যর্থতা উল্লেখ কর।</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 20)।</t>
+          <t>চিরায়ত তরঙ্গ তত্ত্বে শক্তি তরঙ্গের তীব্রতার সমানুপাতিক ধরা হয়; ফলে যেকোনো কম্পাঙ্কের তীব্র আলোতেই ইলেকট্রন নির্গত হওয়ার কথা ছিল, যা সূচনা কম্পাঙ্কের উপস্থিতির পরিপন্থী। দ্বিতীয়ত, তীব্রতা বাড়ালে ইলেকট্রনের বেগ বাড়ার কথা ছিল, কিন্তু বাস্তবে বেগ কেবল কম্পাঙ্কের ওপর নির্ভরশীল। তৃতীয়ত, তরঙ্গ তত্ত্বে তরঙ্গমুখ থেকে শক্তি শোষণ করে ইলেকট্রন নির্গত হতে ঘণ্টার পর ঘণ্টা সময় লাগার কথা ছিল, অথচ বাস্তবে ফোটন আপতনের সাথে সাথে তাৎক্ষণিকভাবে ইলেকট্রন মুক্ত হয়।</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 20</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>(১) আলোক তীব্রতা নয় কম্পাঙ্কের ওপর গতিশক্তি নির্ভর করা, (২) সূচনা কম্পাঙ্কের অস্তিত্ব, (৩) সময়ক্ষেপণহীন তাৎক্ষণিক নিঃসরণ ($&lt; 10^{-9}\text{ s}$)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4685,38 +4430,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>কাল দীর্ঘায়ন ও রকেটের গতিশীল ঘড়ি (সমস্যা 21)</t>
+          <t>কম্পটন ক্রিয়া, দ্য ব্রয় তরঙ্গ ও অনিশ্চয়তা নীতি (Compton &amp; de Broglie)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>[সমস্যা 21: কাল দীর্ঘায়ন ও রকেটের গতিশীল ঘড়ি]
-একটি মহাশূন্যযান ভূমির সাপেক্ষে $v = 0.7c$ বেগে গতিশীল। নভোচারীর ঘড়িতে ১ বছর সময় অতিবাহিত হলে পৃথিবীতে থাকা সহকর্মীদের ঘড়িতে কত বছর সময় পার হবে?</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+কম্পটন বিক্ষেপণে (Compton scattering) একটি এক্স-রে ফোটন একটি স্থির ইলেকট্রনের সাথে সংঘর্ষে লম্ব অভিমুখে ($	heta = 90^\circ$) বিক্ষিপ্ত হলো। বিক্ষিপ্ত ফোটনের তরঙ্গদৈর্ঘ্যের বৃদ্ধি (কম্পটন সরণ $\Delta\lambda$) কত পিকোমিটার? ইলেকট্রনের কম্পটন তরঙ্গদৈর্ঘ্য $\lambda_c$ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 21)।</t>
+          <t>কম্পটন সরণের সমীকরণ: $\Delta\lambda = \lambda' - \lambda = \frac{h}{m_0 c}(1 - \cos\theta)$। ইলেকট্রনের কম্পটন তরঙ্গদৈর্ঘ্য $\lambda_c = \frac{h}{m_0 c} = \frac{6.626 \times 10^{-34}\text{ J}\cdot\text{s}}{(9.11 \times 10^{-31}\text{ kg})(3.0 \times 10^8\text{ m/s})} = \frac{6.626 \times 10^{-34}}{2.733 \times 10^{-22}} \approx 2.426 \times 10^{-12}\text{ m} = 2.426\text{ pm}$। $\theta = 90^\circ$-তে $\cos 90^\circ = 0$, ফলে $\Delta\lambda = \lambda_c(1 - 0) = 2.426\text{ pm}$।</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 21</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>কম্পটন সরণ $\Delta\lambda = \lambda_c = 2.426\text{ pm} = 0.02426\text{ Å}$</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4736,7 +4481,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>দৈর্ঘ্য সংকোচন ও গতিশীল রড (সমস্যা 22)</t>
+          <t>কম্পটন ক্রিয়া, দ্য ব্রয় তরঙ্গ ও অনিশ্চয়তা নীতি (Compton &amp; de Broglie)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4749,25 +4494,25 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>[সমস্যা 22: দৈর্ঘ্য সংকোচন ও গতিশীল রড]
-স্থির অবস্থায় $L_0 = 100\text{ m}$ দীর্ঘ একটি ট্রেন $v = 0.8c$ বেগে প্ল্যাটফর্ম অতিক্রম করছে। প্ল্যাটফর্মের একজন স্থির দর্শকের কাছে ট্রেনের আপাত দৈর্ঘ্য কত মিটার মনে হবে?</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+কম্পটন বিক্ষেপণে সর্বোচ্চ তরঙ্গদৈর্ঘ্য বৃদ্ধি $\Delta\lambda_{\max}$ কোন কোণে ঘটে এবং এর মান কত?</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 22)।</t>
+          <t>$\Delta\lambda = \lambda_c(1 - \cos\theta)$। $1 - \cos\theta$-এর সর্বোচ্চ মান হয় যখন $\cos\theta = -1 \implies \theta = 180^\circ$। ফলে সর্বোচ্চ কম্পটন সরণ $\Delta\lambda_{\max} = 2\lambda_c = 2(2.426\text{ pm}) = 4.852\text{ pm} = 0.0485\text{ Å}$।</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 22</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>$\theta = 180^\circ$ (পশ্চাৎ-বিক্ষেপণ / Backscattering)-এ সর্বোচ্চ বৃদ্ধি $\Delta\lambda_{\max} = 2\lambda_c \approx 4.85\text{ pm}$</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4787,38 +4532,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>আপেক্ষিক ভর ও ভর-শক্তি সমতুল্যতা (সমস্যা 23)</t>
+          <t>কম্পটন ক্রিয়া, দ্য ব্রয় তরঙ্গ ও অনিশ্চয়তা নীতি (Compton &amp; de Broglie)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>[সমস্যা 23: আপেক্ষিক ভর ও ভর-শক্তি সমতুল্যতা]
-একটি কণার গতিশীল ভর এর নিশ্চল ভরের 9 গুণ ($m = 9m_0$)। কণাটির গতিবেগ কত এবং এর মোট আপেক্ষিক শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি ইলেকট্রনকে $V = 100.0\text{ V}$ বিভব পার্থক্যের মধ্য দিয়ে ত্বরাম্বিত করা হলো। ইলেকট্রনটির দ্য ব্রয় (de Broglie) তরঙ্গদৈর্ঘ্য কত অ্যাংস্ট্রম?</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 23)।</t>
+          <t>ইলেকট্রনের ক্ষেত্রে দ্য ব্রয় তরঙ্গদৈর্ঘ্য: $\lambda = \frac{h}{\sqrt{2m e V}} = \frac{1.227}{\sqrt{V}}\text{ nm} = \frac{12.27}{\sqrt{V}}\text{ Å}$। $V = 100\text{ V}$ হলে: $\lambda = \frac{12.27}{\sqrt{100}} = \frac{12.27}{10} = 1.227\text{ Å} = 0.1227\text{ nm}$। (লক্ষণীয় এটি এক্স-রে তরঙ্গদৈর্ঘ্যের সমতুল্য, ফলে ক্রিস্টাল দ্বারা অপবর্তন প্রদর্শন করে)।</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 23</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>দ্য ব্রয় তরঙ্গদৈর্ঘ্য $\lambda = 1.227\text{ Å} = 0.1227\text{ nm}$</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4838,7 +4583,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>আলোকতড়িৎ ক্রিয়া ও নিবৃত্তি বিভব (সমস্যা 24)</t>
+          <t>কম্পটন ক্রিয়া, দ্য ব্রয় তরঙ্গ ও অনিশ্চয়তা নীতি (Compton &amp; de Broglie)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4851,31 +4596,25 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>##PRESET:photoelectric-setup[size:medium]##
-[সমস্যা 24: আলোকতড়িৎ ক্রিয়া ও নিবৃত্তি বিভব]
-##PRESET:photoelectric-setup[size:medium]##
-একটি ধাতব পৃষ্ঠের কার্য অপেক্ষক $W_0 = 6.2\text{ eV}$। ধাতুটির ওপর $\lambda = 2000\text{ \AA}$ তরঙ্গদৈর্ঘ্যের অতিবেগুনি রশ্মি আপতিত হলে নিঃসৃত ফোটো-ইলেকট্রনের সর্বোচ্চ গতিশক্তি ও নিবৃত্তি বিভব ($V_0$) কত?</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি প্রোটন এবং একটি আলফা কণার দ্য ব্রয় তরঙ্গদৈর্ঘ্য সমান হলে তাদের বেগের অনুপাত $v_p : v_lpha$ কত? ($m_lpha pprox 4 m_p$)।</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>##PRESET:photoelectric-setup[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 24)।</t>
+          <t>দ্য ব্রয় তরঙ্গদৈর্ঘ্য $\lambda = \frac{h}{m v}$। তরঙ্গদৈর্ঘ্য সমান হওয়ায় ভরবেগ সমান: $m_p v_p = m_\alpha v_\alpha \implies \frac{v_p}{v_\alpha} = \frac{m_\alpha}{m_p} = \frac{4 m_p}{m_p} = 4$। অর্থাৎ $v_p : v_\alpha = 4 : 1$।</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 24</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+          <t>$v_p : v_\alpha = 4 : 1$</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4895,38 +4634,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ডি-ব্রগলী তরঙ্গদৈর্ঘ্য ও ইলেকট্রনের বেগ (সমস্যা 25)</t>
+          <t>কম্পটন ক্রিয়া, দ্য ব্রয় তরঙ্গ ও অনিশ্চয়তা নীতি (Compton &amp; de Broglie)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>[সমস্যা 25: ডি-ব্রগলী তরঙ্গদৈর্ঘ্য ও ইলেকট্রনের বেগ]
-একটি ইলেকট্রনকে $V = 700\text{ V}$ বিভব পার্থক্যের মধ্য দিয়ে ত্বরান্বিত করা হলো। ইলেকট্রনটির সাথে সংশ্লিষ্ট ডি-ব্রগলী তরঙ্গদৈর্ঘ্য ($\lambda = \frac{12.27}{\sqrt{V}}\text{ \AA}$) কত?</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+তাপীয় নিউট্রনের (Thermal neutron at $T = 300\text{ K}$) গড় গতিশক্তি $K = rac{3}{2}k_B T$। এই নিউট্রনের দ্য ব্রয় তরঙ্গদৈর্ঘ্য কত? ($m_n = 1.675 \times 10^{-27}\text{ kg}, k_B = 1.38 \times 10^{-23}\text{ J/K}$)।</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 25)।</t>
+          <t>গতিশক্তি $K = 1.5(1.38 \times 10^{-23})(300) = 6.21 \times 10^{-21}\text{ J}$। ভরবেগ $p = \sqrt{2m_n K} = \sqrt{2(1.675 \times 10^{-27})(6.21 \times 10^{-21})} = \sqrt{2.080 \times 10^{-47}} \approx 3.725 \times 10^{-24}\text{ kg}\cdot\text{m/s}$। তরঙ্গদৈর্ঘ্য $\lambda = \frac{h}{p} = \frac{6.626 \times 10^{-34}}{3.725 \times 10^{-24}} \approx 1.779 \times 10^{-10}\text{ m} = 1.78\text{ Å}$।</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 25</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+          <t>তরঙ্গদৈর্ঘ্য $\lambda = 1.78\text{ Å} = 0.178\text{ nm}$</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4946,7 +4685,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>কম্পটন সরণ ও ফোটন বিচ্ছুরণ (সমস্যা 26)</t>
+          <t>কম্পটন ক্রিয়া, দ্য ব্রয় তরঙ্গ ও অনিশ্চয়তা নীতি (Compton &amp; de Broglie)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4959,25 +4698,25 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>[সমস্যা 26: কম্পটন সরণ ও ফোটন বিচ্ছুরণ]
-একটি এক্স-রে ফোটন একটি স্থির ইলেকট্রনের সাথে সংঘর্ষে লিপ্ত হয়ে $\theta = 80^\circ$ কোণে বিক্ষিপ্ত হলো। ফোটনটির তরঙ্গদৈর্ঘ্যের কম্পটন বৃদ্ধি $\Delta\lambda = \frac{h}{m_0 c}(1 - \cos\theta)$ কত আর্মস্ট্রং?</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+হাইজেনবার্গের অনিশ্চয়তা নীতি অনুসারে একটি ইলেকট্রনের অবস্থানের অনিশ্চয়তা $\Delta x = 1.0 	imes 10^{-10}\text{ m}$ (পরমাণুর আকারের সমান)। এর ভরবেগের ন্যূনতম অনিশ্চয়তা $\Delta p$ এবং বেগের অনিশ্চয়তা $\Delta v$ কত? ($\hbar = rac{h}{2\pi} pprox 1.055 \times 10^{-34}\text{ J}\cdot\text{s}$)।</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 26)।</t>
+          <t>অনিশ্চয়তা নীতি: $\Delta x \Delta p \ge \frac{\hbar}{2} \implies \Delta p_{\min} = \frac{1.055 \times 10^{-34}}{2(1.0 \times 10^{-10})} = 5.275 \times 10^{-25}\text{ kg}\cdot\text{m/s}$। বেগের অনিশ্চয়তা $\Delta v = \frac{\Delta p}{m_e} = \frac{5.275 \times 10^{-25}}{9.11 \times 10^{-31}} \approx 5.79 \times 10^5\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 26</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+          <t>ভরবেগের অনিশ্চয়তা $\Delta p = 5.27 \times 10^{-25}\text{ kg}\cdot\text{m/s}$, বেগের অনিশ্চয়তা $\Delta v = 5.79 \times 10^5\text{ m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4997,38 +4736,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>এক্স-রে নলের কাট-অফ তরঙ্গদৈর্ঘ্য (সমস্যা 27)</t>
+          <t>কম্পটন ক্রিয়া, দ্য ব্রয় তরঙ্গ ও অনিশ্চয়তা নীতি (Compton &amp; de Broglie)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>[সমস্যা 27: এক্স-রে নলের কাট-অফ তরঙ্গদৈর্ঘ্য]
-একটি কুলিজ নলে $V = 90\text{ kV}$ বিভব প্রযুক্ত থাকলে উৎপন্ন এক্স-রের ন্যূনতম তরঙ্গদৈর্ঘ্য (Cut-off wavelength, $\lambda_{min} = \frac{hc}{eV}$) কত?</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+কেন একটি মুক্ত ইলেকট্রন পরমাণুর নিউক্লিয়াসের ভেতরে অবস্থান করতে পারে না—হাইজেনবার্গের অনিশ্চয়তা নীতির সাহায্যে প্রমাণ কর।</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 27)।</t>
+          <t>নিউক্লিয়াসের ব্যাস $\approx 10^{-14}\text{ m}$। যদি ইলেকট্রন নিউক্লিয়াসে আবদ্ধ থাকত, তবে $\Delta p \approx \frac{\hbar}{\Delta x} \approx \frac{1.055 \times 10^{-34}}{10^{-14}} \approx 1.05 \times 10^{-20}\text{ kg}\cdot\text{m/s}$। এই ভরবেগের ক্ষেত্রে আপেক্ষিক শক্তি $E \approx p c \approx (1.05 \times 10^{-20})(3 \times 10^8) \approx 3.16 \times 10^{-12}\text{ J} \approx 20\text{ MeV}$। কিন্তু তেজস্ক্রিয় $\beta$-ক্ষয়ে নির্গত ইলেকট্রনের শক্তি সর্বোচ্চ ২-৩ MeV হয়। সুতরাং কোনো স্থায়ী মুক্ত ইলেকট্রন নিউক্লিয়াসের অভ্যন্তরে থাকতে পারে না।</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 27</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+          <t>নিউক্লিয়াসের আকারের সীমার মধ্যে ($\Delta x \approx 10^{-14}\text{ m}$) অবস্থান করলে ইলেকট্রনের প্রয়োজনীয় গতিশক্তি $\approx 20\text{ MeV}$ হয়, যা বাস্তবে পর্যবেক্ষণকৃত শক্তির সাথে অসঙ্গতিপূর্ণ</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5048,7 +4787,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>হাইজেনবার্গের অনিশ্চয়তা নীতি (সমস্যা 28)</t>
+          <t>কম্পটন ক্রিয়া, দ্য ব্রয় তরঙ্গ ও অনিশ্চয়তা নীতি (Compton &amp; de Broglie)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5061,25 +4800,25 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>[সমস্যা 28: হাইজেনবার্গের অনিশ্চয়তা নীতি]
-একটি গতিশীল ইলেকট্রনের অবস্থান পরিমাপে অনিশ্চয়তা $\Delta x = 0.6\text{ nm}$। হাইজেনবার্গের অনিশ্চয়তা নীতিানুসারে ইলেকট্রনটির ভরবেগ পরিমাপে ন্যূনতম অনিশ্চয়তা কত?</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+ডেভিসন-জার্মার পরীক্ষায় (Davisson-Germer Experiment) $V = 54\text{ V}$ বিভবে ত্বরান্বিত ইলেকট্রন নিকেল স্ফটিকের ওপর আপতিত হয়ে $	heta = 50^\circ$ কোণে অপবর্তন চরম গঠন করে। নিকেলের পরমাণু তলের ব্যবধান $d = 0.91\text{ Å}$ হলে ব্র্যাগের সূত্রানুযায়ী এবং দ্য ব্রয় সূত্রানুযায়ী তরঙ্গদৈর্ঘ্যের তুলনা কর।</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 28)।</t>
+          <t>ব্র্যাগের প্রতিফলক কোণ $\theta' = \frac{180^\circ - 50^\circ}{2} = 65^\circ$। ব্র্যাগের সূত্র ($n = 1$): $\lambda = 2d\sin\theta' = 2(0.91\text{ Å})\sin 65^\circ = 1.82 \times 0.9063 \approx 1.65\text{ Å}$। দ্য ব্রয়ের তাত্ত্বিক সূত্র: $\lambda = \frac{12.27}{\sqrt{54}} = \frac{12.27}{7.348} \approx 1.67\text{ Å}$। এই দুই মান প্রায় অভিন্ন হওয়ায় এটি ইলেকট্রনের তরঙ্গ প্রকৃতির প্রথম অকাট্য পরীক্ষামূলক প্রমাণ দেয়।</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 28</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+          <t>ব্র্যাগের সূত্র হতে $\lambda = 1.65\text{ Å}$, দ্য ব্রয় সূত্র হতে $\lambda = 1.67\text{ Å}$ (চমৎকার সংগতিপূর্ণ)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5099,38 +4838,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ভর ত্রুটি হতে উৎপন্ন শক্তির পরিমাণ (সমস্যা 29)</t>
+          <t>কম্পটন ক্রিয়া, দ্য ব্রয় তরঙ্গ ও অনিশ্চয়তা নীতি (Compton &amp; de Broglie)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>[সমস্যা 29: ভর ত্রুটি হতে উৎপন্ন শক্তির পরিমাণ]
-একটি পারমাণবিক ফিশন বিক্রিয়ায় $1\text{ g}$ ভর সম্পূর্ণরূপে শক্তিতে রূপান্তরিত হলে আইনস্টাইনের সমীকরণ $E = mc^2$ অনুযায়ী কত জুল বা কিলোওয়াট-ঘণ্টা শক্তি নির্গত হবে?</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি ফোটনের শক্তি এবং একটি ইলেকট্রনের গতিশক্তি সমান ($E_p = K_e = 100\text{ eV}$)। তাদের দ্য ব্রয় তরঙ্গদৈর্ঘ্যের অনুপাত $\lambda_p / \lambda_e$ কত?</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 29)।</t>
+          <t>ফোটনের জন্য: $\lambda_p = \frac{h c}{E} = \frac{1240\text{ eV}\cdot\text{nm}}{100\text{ eV}} = 12.4\text{ nm}$। ইলেকট্রনের জন্য: $\lambda_e = \frac{1.227}{\sqrt{100}}\text{ nm} = 0.1227\text{ nm}$। অনুপাত $\frac{\lambda_p}{\lambda_e} = \frac{12.4}{0.1227} \approx 101.06 \approx 101.0$। (ফোটনের তরঙ্গদৈর্ঘ্য ইলেকট্রনের চেয়ে প্রায় ১০০ গুণ বেশি)।</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 29</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+          <t>$\lambda_p / \lambda_e = 101.0$</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5150,7 +4889,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>সূচনা কম্পাঙ্ক ও কার্য-অপেক্ষক (সমস্যা 30)</t>
+          <t>কম্পটন ক্রিয়া, দ্য ব্রয় তরঙ্গ ও অনিশ্চয়তা নীতি (Compton &amp; de Broglie)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5163,25 +4902,25 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>[সমস্যা 30: সূচনা কম্পাঙ্ক ও কার্য-অপেক্ষক]
-সিজিয়াম ধাতুর সূচনা তরঙ্গদৈর্ঘ্য $\lambda_0 = 8500\text{ \AA}$। ধাতুটির কার্য-অপেক্ষক ($W_0 = hc/\lambda_0$) ইলেকট্রন-ভোল্ট (eV) এককে নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+তরঙ্গ-কণা দ্বৈততা (Wave-Particle Duality) এবং বোরের পরিপূরক নীতি (Bohr's Principle of Complementarity) বলতে কী বোঝায়?</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 30)।</t>
+          <t>আলোর ব্যতিচার ও অপবর্তন পরীক্ষা এর বিশুদ্ধ তরঙ্গ রূপ প্রমাণ করে, যেখানে আলোক তড়িৎ ক্রিয়া ও কম্পটন প্রভাব এর বিশুদ্ধ কণা (ফোটন) রূপ প্রমাণ করে। বোরের পরিপূরক নীতি বলে যে কোনো পদার্থ বা বিকিরণ একই সাথে সম্পূর্ণ বিবরণ দিতে তরঙ্গ ও কণা উভয়ের প্রয়োজন হলেও কোনো একক পরীক্ষামূলক সেটআপে এরা কখনোই একসাথে যুগপৎ আবির্ভূত হয় না।</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 30</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+          <t>আলো বা বস্তু যুগপৎ তরঙ্গ ও কণা উভয় প্রকৃতির; তবে কোনো একক পরীক্ষায় একই সাথে এই দুই রূপ প্রকাশ পায় না, এরা একে অপরের পরিপূরক</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5201,38 +4940,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>কাল দীর্ঘায়ন ও রকেটের গতিশীল ঘড়ি (সমস্যা 31)</t>
+          <t>উন্নত আপেক্ষিক বলবিদ্যা ও কোয়ান্টাম ডায়নামিক্স (Advanced Relativistic &amp; Quantum)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>[সমস্যা 31: কাল দীর্ঘায়ন ও রকেটের গতিশীল ঘড়ি]
-একটি মহাশূন্যযান ভূমির সাপেক্ষে $v = 0.9c$ বেগে গতিশীল। নভোচারীর ঘড়িতে ১ বছর সময় অতিবাহিত হলে পৃথিবীতে থাকা সহকর্মীদের ঘড়িতে কত বছর সময় পার হবে?</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি ইলেকট্রন কত বেগে গতিশীল হলে এর আপেক্ষিক গতিশক্তি তার স্থির ভর শক্তির সমান ($K = E_0$) হবে?</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 31)।</t>
+          <t>মোট শক্তি $E = K + E_0 = E_0 + E_0 = 2 E_0$। আবার $E = \gamma E_0 \implies \gamma = 2$। $\frac{1}{\sqrt{1 - v^2/c^2}} = 2 \implies 1 - \frac{v^2}{c^2} = \frac{1}{4} \implies \frac{v^2}{c^2} = \frac{3}{4} \implies v = \frac{\sqrt{3}}{2} c \approx 0.866 c$।</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 31</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>বেগ $v = \frac{\sqrt{3}}{2} c \approx 0.866 c$</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5252,12 +4991,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>দৈর্ঘ্য সংকোচন ও গতিশীল রড (সমস্যা 32)</t>
+          <t>উন্নত আপেক্ষিক বলবিদ্যা ও কোয়ান্টাম ডায়নামিক্স (Advanced Relativistic &amp; Quantum)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -5265,25 +5004,25 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>[সমস্যা 32: দৈর্ঘ্য সংকোচন ও গতিশীল রড]
-স্থির অবস্থায় $L_0 = 100\text{ m}$ দীর্ঘ একটি ট্রেন $v = 0.6c$ বেগে প্ল্যাটফর্ম অতিক্রম করছে। প্ল্যাটফর্মের একজন স্থির দর্শকের কাছে ট্রেনের আপাত দৈর্ঘ্য কত মিটার মনে হবে?</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি প্রোটনের ($m_0 = 1.67 \times 10^{-27}\text{ kg}$) আপেক্ষিক ভরবেগ $p = m_0 c$ হলে প্রোটনটির বেগ কত?</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 32)।</t>
+          <t>আপেক্ষিক ভরবেগ $p = \gamma m_0 v = m_0 c \implies \gamma v = c \implies \frac{v}{\sqrt{1 - v^2/c^2}} = c$। বর্গ করে: $\frac{v^2}{1 - v^2/c^2} = c^2 \implies v^2 = c^2 - v^2 \implies 2v^2 = c^2 \implies v = \frac{c}{\sqrt{2}} \approx 0.707 c$।</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 32</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+          <t>বেগ $v = \frac{1}{\sqrt{2}} c \approx 0.707 c$</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5303,38 +5042,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>আপেক্ষিক ভর ও ভর-শক্তি সমতুল্যতা (সমস্যা 33)</t>
+          <t>উন্নত আপেক্ষিক বলবিদ্যা ও কোয়ান্টাম ডায়নামিক্স (Advanced Relativistic &amp; Quantum)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>[সমস্যা 33: আপেক্ষিক ভর ও ভর-শক্তি সমতুল্যতা]
-একটি কণার গতিশীল ভর এর নিশ্চল ভরের 7 গুণ ($m = 7m_0$)। কণাটির গতিবেগ কত এবং এর মোট আপেক্ষিক শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি চলমান কণার মোট শক্তি $E$ এবং ভরবেগ $p$ জানা থাকলে কণাটির দ্রুতি $v = rac{p c^2}{E}$ প্রমাণ কর।</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 33)।</t>
+          <t>আমরা জানি $p = \gamma m_0 v$ এবং $E = \gamma m_0 c^2$। ভাগ করে: $\frac{p}{E} = \frac{\gamma m_0 v}{\gamma m_0 c^2} = \frac{v}{c^2} \implies v = \frac{p c^2}{E}$। এটি যেকোনো আপেক্ষিক কণার জন্য সর্বদা প্রযোজ্য।</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 33</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+          <t>$v = \frac{p c^2}{E}$</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5354,12 +5093,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>আলোকতড়িৎ ক্রিয়া ও নিবৃত্তি বিভব (সমস্যা 34)</t>
+          <t>উন্নত আপেক্ষিক বলবিদ্যা ও কোয়ান্টাম ডায়নামিক্স (Advanced Relativistic &amp; Quantum)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -5367,31 +5106,25 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>##PRESET:photoelectric-setup[size:medium]##
-[সমস্যা 34: আলোকতড়িৎ ক্রিয়া ও নিবৃত্তি বিভব]
-##PRESET:photoelectric-setup[size:medium]##
-একটি ধাতব পৃষ্ঠের কার্য অপেক্ষক $W_0 = 8.2\text{ eV}$। ধাতুটির ওপর $\lambda = 6000\text{ \AA}$ তরঙ্গদৈর্ঘ্যের অতিবেগুনি রশ্মি আপতিত হলে নিঃসৃত ফোটো-ইলেকট্রনের সর্বোচ্চ গতিশক্তি ও নিবৃত্তি বিভব ($V_0$) কত?</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি সৌর পাল (Solar sail) মহাকাশযানের পালের ক্ষেত্রফল $A = 1.0 	imes 10^4\text{ m}^2$। সূর্য হতে আলোর তীব্রতা $I = 1400\text{ W/m}^2$ এবং পালটি সম্পূর্ণ প্রতিফলক ($R = 1.0$)। মহাকাশযানের ওপর সূর্যের বিকিরণ চাপ (Radiation pressure $P_{\text{rad}}$) এবং মোট বিকিরণ বল কত নিউটন?</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>##PRESET:photoelectric-setup[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 34)।</t>
+          <t>নিখুঁত প্রতিফলনে বিকিরণ চাপ $P_{\text{rad}} = \frac{2I}{c} = \frac{2 \times 1400}{3.0 \times 10^8} = \frac{2800}{3.0 \times 10^8} \approx 9.333 \times 10^{-6}\text{ N/m}^2$। মোট বল $F = P_{\text{rad}} \times A = (9.333 \times 10^{-6}\text{ N/m}^2) \times (1.0 \times 10^4\text{ m}^2) \approx 0.0933\text{ N}$।</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 34</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>বিকিরণ চাপ $P_{\text{rad}} = 9.33 \times 10^{-6}\text{ N/m}^2$, মোট বল $F = 0.0933\text{ N}$</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5411,38 +5144,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ডি-ব্রগলী তরঙ্গদৈর্ঘ্য ও ইলেকট্রনের বেগ (সমস্যা 35)</t>
+          <t>উন্নত আপেক্ষিক বলবিদ্যা ও কোয়ান্টাম ডায়নামিক্স (Advanced Relativistic &amp; Quantum)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>[সমস্যা 35: ডি-ব্রগলী তরঙ্গদৈর্ঘ্য ও ইলেকট্রনের বেগ]
-একটি ইলেকট্রনকে $V = 900\text{ V}$ বিভব পার্থক্যের মধ্য দিয়ে ত্বরান্বিত করা হলো। ইলেকট্রনটির সাথে সংশ্লিষ্ট ডি-ব্রগলী তরঙ্গদৈর্ঘ্য ($\lambda = \frac{12.27}{\sqrt{V}}\text{ \AA}$) কত?</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি ফোটনের প্রারম্ভিক তরঙ্গদৈর্ঘ্য $\lambda = 0.0200\text{ Å}$। এটি একটি স্থির ইলেকট্রনের সাথে সংঘর্ষে $60^\circ$ কোণে বিক্ষিপ্ত হলে বিক্ষিপ্ত ফোটনের তরঙ্গদৈর্ঘ্য $\lambda'$ এবং প্রতিক্ষিপ্ত ইলেকট্রনের অর্জিত গতিশক্তি কত $\text{keV}$?</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 35)।</t>
+          <t>কম্পটন সরণ $\Delta\lambda = \lambda_c(1 - \cos 60^\circ) = 0.02426(1 - 0.5) = 0.01213\text{ Å}$। বিক্ষিপ্ত তরঙ্গদৈর্ঘ্য $\lambda' = \lambda + \Delta\lambda = 0.0200 + 0.01213 = 0.03213\text{ Å}$। আপতিত ফোটনের শক্তি $E = \frac{12.4\text{ keV}\cdot\text{Å}}{0.0200\text{ Å}} = 620.0\text{ keV}$। বিক্ষিপ্ত ফোটনের শক্তি $E' = \frac{12.4}{0.03213} \approx 385.9\text{ keV}$। ইলেকট্রনের গতিশক্তি $K_e = E - E' = 620.0 - 385.9 = 234.1\text{ keV}$।</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 35</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>বিক্ষিপ্ত ফোটনের $\lambda' = 0.03213\text{ Å}$, ইলেকট্রনের গতিশক্তি $K_e = 233.1\text{ keV}$</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5462,12 +5195,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>কম্পটন সরণ ও ফোটন বিচ্ছুরণ (সমস্যা 36)</t>
+          <t>উন্নত আপেক্ষিক বলবিদ্যা ও কোয়ান্টাম ডায়নামিক্স (Advanced Relativistic &amp; Quantum)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -5475,25 +5208,25 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>[সমস্যা 36: কম্পটন সরণ ও ফোটন বিচ্ছুরণ]
-একটি এক্স-রে ফোটন একটি স্থির ইলেকট্রনের সাথে সংঘর্ষে লিপ্ত হয়ে $\theta = 60^\circ$ কোণে বিক্ষিপ্ত হলো। ফোটনটির তরঙ্গদৈর্ঘ্যের কম্পটন বৃদ্ধি $\Delta\lambda = \frac{h}{m_0 c}(1 - \cos\theta)$ কত আর্মস্ট্রং?</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি $m = 1000\text{ kg}$ ভরের গাড়ি $108\text{ km/h}$ বেগে চলছে। গাড়িটির দ্য ব্রয় তরঙ্গদৈর্ঘ্য নির্ণয় কর এবং কেন ম্যাক্রোস্কোপিক জগতে তরঙ্গ ধর্ম পরিলক্ষিত হয় না ব্যাখ্যা কর।</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 36)।</t>
+          <t>বেগ $v = \frac{108 \times 1000}{3600} = 30\text{ m/s}$। ভরবেগ $p = mv = 1000 \times 30 = 30000\text{ kg}\cdot\text{m/s}$। দ্য ব্রয় তরঙ্গদৈর্ঘ্য $\lambda = \frac{h}{p} = \frac{6.626 \times 10^{-34}}{30000} \approx 2.209 \times 10^{-38}\text{ m}$। এই তরঙ্গদৈর্ঘ্য কোনো পরিচিত পারমাণবিক বা নিউক্লিয়ার স্কেলের ($10^{-15}\text{ m}$) চেয়েও বহু গুণ ক্ষুদ্র হওয়ায় এর কোনো অপবর্তন বা ব্যতিচার বাস্তবে কখনোই শনাক্তযোগ্য হয় না।</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 36</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>তরঙ্গদৈর্ঘ্য $\lambda = 2.21 \times 10^{-38}\text{ m}$ (পরমাণুর চেয়েও কোটি কোটি গুণ ক্ষুদ্র)</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5513,38 +5246,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>এক্স-রে নলের কাট-অফ তরঙ্গদৈর্ঘ্য (সমস্যা 37)</t>
+          <t>উন্নত আপেক্ষিক বলবিদ্যা ও কোয়ান্টাম ডায়নামিক্স (Advanced Relativistic &amp; Quantum)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>[সমস্যা 37: এক্স-রে নলের কাট-অফ তরঙ্গদৈর্ঘ্য]
-একটি কুলিজ নলে $V = 70\text{ kV}$ বিভব প্রযুক্ত থাকলে উৎপন্ন এক্স-রের ন্যূনতম তরঙ্গদৈর্ঘ্য (Cut-off wavelength, $\lambda_{min} = \frac{hc}{eV}$) কত?</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+টুইন প্যারাডক্স (Twin Paradox): দুই যমজ ভাইয়ের একজন পৃথিবীতে রইল এবং অপরজন $0.95 c$ বেগে দূরবর্তী গ্রহে গিয়ে ২০ বছর পর (যাত্রীর ঘড়ি অনুযায়ী) ফিরে এলো। ফিরে আসার পর তাদের বয়সের পার্থক্য কত হবে?</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 37)।</t>
+          <t>ভ্রমণকারী ভাইয়ের নিজস্ব সময় $t_0 = 20\text{ বছর}$। লরেন্টজ গুণক $\gamma = \frac{1}{\sqrt{1 - 0.95^2}} = \frac{1}{\sqrt{1 - 0.9025}} = \frac{1}{\sqrt{0.0975}} \approx \frac{1}{0.31225} \approx 3.2026$। পৃথিবীতে অতিক্রান্ত সময় $t = \gamma t_0 = 3.2026 \times 20 \approx 64.05\text{ বছর}$। ভ্রমণকারী ভাই ফিরে এলে দেখবে পৃথিবীর ভাই তার চেয়ে $64.05 - 20 = 44.05$ বছরের বড় হয়ে গেছে। ভ্রমণকারী ভাইয়ের দিকে ত্বরণ ও দিক পরিবর্তনের কারণে প্রতিসাম্য ভেঙে এটি একটি বাস্তব ভৌত ঘটনা।</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 37</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>পৃথিবীর ভাইয়ের বয়স বৃদ্ধি পাবে $64.05$ বছর; ফলে ভ্রমণকারী ভাই ৪৪ বছরের ছোট থাকবে</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5564,12 +5297,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>হাইজেনবার্গের অনিশ্চয়তা নীতি (সমস্যা 38)</t>
+          <t>উন্নত আপেক্ষিক বলবিদ্যা ও কোয়ান্টাম ডায়নামিক্স (Advanced Relativistic &amp; Quantum)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -5577,25 +5310,25 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>[সমস্যা 38: হাইজেনবার্গের অনিশ্চয়তা নীতি]
-একটি গতিশীল ইলেকট্রনের অবস্থান পরিমাপে অনিশ্চয়তা $\Delta x = 0.8\text{ nm}$। হাইজেনবার্গের অনিশ্চয়তা নীতিানুসারে ইলেকট্রনটির ভরবেগ পরিমাপে ন্যূনতম অনিশ্চয়তা কত?</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি কৃষ্ণবস্তুর বিকিরণে প্ল্যাঙ্কের কোয়ান্টাম প্রকল্প: প্লাঙ্ক কীভাবে ম্যাক্সওয়েল-বোল্টজম্যানের অবিচ্ছিন্ন শক্তি ধারণাকে ভেঙে শক্তিকে ফোটন কোয়ান্টায় ($E = n h f$) রূপ দিয়ে আল্ট্রাভায়োলেট বিপর্যয় (Ultraviolet Catastrophe) সমাধান করেছিলেন?</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 38)।</t>
+          <t>চিরায়ত র্যালে-জিন্স সূত্রে ক্ষুদ্র তরঙ্গদৈর্ঘ্যে শক্তি ঘনত্ব অসীমে ধাবিত হতো ($\rho(\lambda) \propto \lambda^{-4}$, যা আল্ট্রাভায়োলেট বিপর্যয় নামে পরিচিত)। প্লাঙ্ক প্রস্তাব করেন কম্পাঙ্ক বৃদ্ধির সাথে সাথে কোয়ান্টামের শক্তি $h f$ এত বিশাল হয় যে উচ্চ শক্তিতে অসিলেটর উত্তেজিত হওয়ার সম্ভাবনা বোল্টজম্যান ফ্যাক্টর $e^{-hf/k_B T}$ দ্বারা তীব্রভাবে হ্রাস পায়। ফলে উচ্চ কম্পাঙ্কে বিকিরণ শূন্যে নেমে আসে এবং কৃষ্ণবস্তুর বর্ণালী নির্ভুলভাবে ব্যাখ্যা পায়।</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 38</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+          <t>শক্তি অবিচ্ছিন্নভাবে নয় বরং নির্দিষ্ট শক্তি প্যাকেট বা কোয়ান্টায় শোষিত ও বিকিরিত হয় ($E = h f$)</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5615,38 +5348,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ভর ত্রুটি হতে উৎপন্ন শক্তির পরিমাণ (সমস্যা 39)</t>
+          <t>উন্নত আপেক্ষিক বলবিদ্যা ও কোয়ান্টাম ডায়নামিক্স (Advanced Relativistic &amp; Quantum)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>[সমস্যা 39: ভর ত্রুটি হতে উৎপন্ন শক্তির পরিমাণ]
-একটি পারমাণবিক ফিশন বিক্রিয়ায় $1\text{ g}$ ভর সম্পূর্ণরূপে শক্তিতে রূপান্তরিত হলে আইনস্টাইনের সমীকরণ $E = mc^2$ অনুযায়ী কত জুল বা কিলোওয়াট-ঘণ্টা শক্তি নির্গত হবে?</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি এক্স-রে টিউবে অ্যানোড ও ক্যাথোডের বিভব পার্থক্য $V = 50.0\text{ kV}$। টিউব হতে নির্গত এক্স-রে ফোটনের ন্যূনতম তরঙ্গদৈর্ঘ্য (Cut-off wavelength $\lambda_{\min}$) কত?</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 39)।</t>
+          <t>ডুয়ান-হান্ট সূত্র (Duane-Hunt Law): সমস্ত বৈদ্যুতিক শক্তি একটি মাত্র ফোটনে রূপান্তরিত হলে তরঙ্গদৈর্ঘ্য ন্যূনতম হয়: $e V = \frac{h c}{\lambda_{\min}} \implies \lambda_{\min} = \frac{h c}{e V} = \frac{12.4\text{ keV}\cdot\text{Å}}{50.0\text{ keV}} = 0.248\text{ Å} = 24.8\text{ pm}$।</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 39</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+          <t>ন্যূনতম তরঙ্গদৈর্ঘ্য $\lambda_{\min} = 0.248\text{ Å} = 24.8\text{ pm}$</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5666,12 +5399,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>সূচনা কম্পাঙ্ক ও কার্য-অপেক্ষক (সমস্যা 40)</t>
+          <t>উন্নত আপেক্ষিক বলবিদ্যা ও কোয়ান্টাম ডায়নামিক্স (Advanced Relativistic &amp; Quantum)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -5679,25 +5412,25 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>[সমস্যা 40: সূচনা কম্পাঙ্ক ও কার্য-অপেক্ষক]
-সিজিয়াম ধাতুর সূচনা তরঙ্গদৈর্ঘ্য $\lambda_0 = 6500\text{ \AA}$। ধাতুটির কার্য-অপেক্ষক ($W_0 = hc/\lambda_0$) ইলেকট্রন-ভোল্ট (eV) এককে নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি অতিবেগুনী লেজারের ক্ষমতা $P = 10.0\text{ mW}$ এবং তরঙ্গদৈর্ঘ্য $\lambda = 250\text{ nm}$। লেজার রশ্মি একটি ধাতব পাতে ($W_0 = 2.2\text{ eV}$) আপতিত হলে প্রতি সেকেন্ডে সর্বোচ্চ কত অ্যাম্পিয়ার ফটো-কারেন্ট উৎপন্ন হতে পারে? (কোয়ান্টাম দক্ষতা $1.0\%$ ধর)।</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 40)।</t>
+          <t>একটি ফোটনের শক্তি $E_p = \frac{1240}{250} = 4.96\text{ eV} = 7.936 \times 10^{-19}\text{ J}$। প্রতি সেকেন্ডে আপতিত ফোটন $N_p = \frac{0.010\text{ W}}{7.936 \times 10^{-19}\text{ J}} \approx 1.26 \times 10^{16}\text{ s}^{-1}$। ১% ফোটন ইলেকট্রন মুক্ত করলে নির্গত ইলেকট্রন হার $N_e = 0.01 N_p = 1.26 \times 10^{14}\text{ s}^{-1}$। কারেন্ট $I = N_e e = (1.26 \times 10^{14}) \times (1.6 \times 10^{-19}\text{ C}) \approx 2.016 \times 10^{-5}\text{ A} \approx 20.16\text{ }\mu\text{A}$।</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 40</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+          <t>সম্পৃক্ত কারেন্ট $I = 2.01 \times 10^{-5}\text{ A} = 20.1\text{ }\mu\text{A}$</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5717,38 +5450,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>কাল দীর্ঘায়ন ও রকেটের গতিশীল ঘড়ি (সমস্যা 41)</t>
+          <t>উন্নত আধুনিক পদার্থবিজ্ঞান সংশ্লেষণ ও তাত্ত্বিক প্রমাণ (Modern Physics Synthesis)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>[সমস্যা 41: কাল দীর্ঘায়ন ও রকেটের গতিশীল ঘড়ি]
-একটি মহাশূন্যযান ভূমির সাপেক্ষে $v = 0.7c$ বেগে গতিশীল। নভোচারীর ঘড়িতে ১ বছর সময় অতিবাহিত হলে পৃথিবীতে থাকা সহকর্মীদের ঘড়িতে কত বছর সময় পার হবে?</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি গতিশীল রকেটের ঘড়ি পৃথিবীর ঘড়ির চেয়ে $1\%$ ধীরে চলে। রকেটের দ্রুতি কত?</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 41)।</t>
+          <t>সময় দীর্ঘায়নের অনুপাত: $\frac{t_0}{t} = \sqrt{1 - v^2/c^2} = 1 - 0.01 = 0.99$। বর্গ করে: $1 - \frac{v^2}{c^2} = 0.99^2 = 0.9801 \implies \frac{v^2}{c^2} = 0.0199 \implies v = \sqrt{0.0199} c \approx 0.14107 c \approx 4.23 \times 10^7\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 41</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+          <t>রকেটের দ্রুতি $v = 0.141 c \approx 4.23 \times 10^7\text{ m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5768,12 +5501,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>দৈর্ঘ্য সংকোচন ও গতিশীল রড (সমস্যা 42)</t>
+          <t>উন্নত আধুনিক পদার্থবিজ্ঞান সংশ্লেষণ ও তাত্ত্বিক প্রমাণ (Modern Physics Synthesis)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -5781,25 +5514,25 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>[সমস্যা 42: দৈর্ঘ্য সংকোচন ও গতিশীল রড]
-স্থির অবস্থায় $L_0 = 100\text{ m}$ দীর্ঘ একটি ট্রেন $v = 0.8c$ বেগে প্ল্যাটফর্ম অতিক্রম করছে। প্ল্যাটফর্মের একজন স্থির দর্শকের কাছে ট্রেনের আপাত দৈর্ঘ্য কত মিটার মনে হবে?</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি কণার গতিশক্তি তার মোট শক্তির $75\%$ হলে কণাটির দ্রুতি আলোর দ্রুতির কত গুণ?</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 42)।</t>
+          <t>$K = 0.75 E \implies E_0 = E - K = 0.25 E \implies E = 4 E_0$। $\gamma = 4 \implies \sqrt{1 - v^2/c^2} = \frac{1}{4} \implies 1 - \frac{v^2}{c^2} = \frac{1}{16} \implies \frac{v^2}{c^2} = \frac{15}{16} \implies v = \frac{\sqrt{15}}{4} c \approx 0.9682 c$।</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 42</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>দ্রুতি $v = \frac{\sqrt{15}}{4} c \approx 0.968 c$</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5819,38 +5552,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>আপেক্ষিক ভর ও ভর-শক্তি সমতুল্যতা (সমস্যা 43)</t>
+          <t>উন্নত আধুনিক পদার্থবিজ্ঞান সংশ্লেষণ ও তাত্ত্বিক প্রমাণ (Modern Physics Synthesis)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>[সমস্যা 43: আপেক্ষিক ভর ও ভর-শক্তি সমতুল্যতা]
-একটি কণার গতিশীল ভর এর নিশ্চল ভরের 9 গুণ ($m = 9m_0$)। কণাটির গতিবেগ কত এবং এর মোট আপেক্ষিক শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি কণার ভরবেগ $p = 1.0\text{ GeV/c}$ এবং স্থির ভর $m_0 = 0.5\text{ GeV/c}^2$ হলে কণাটির মোট শক্তি $E$ এবং গতিশক্তি $K$ কত $\text{GeV}$?</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 43)।</t>
+          <t>$E = \sqrt{p^2 c^2 + m_0^2 c^4} = \sqrt{1.0^2 + 0.5^2} = \sqrt{1.0 + 0.25} = \sqrt{1.25} \approx 1.118\text{ GeV}$। গতিশক্তি $K = E - E_0 = 1.118 - 0.50 = 0.618\text{ GeV}$।</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 43</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+          <t>মোট শক্তি $E = 1.118\text{ GeV}$, গতিশক্তি $K = 0.618\text{ GeV}$</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5870,12 +5603,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>আলোকতড়িৎ ক্রিয়া ও নিবৃত্তি বিভব (সমস্যা 44)</t>
+          <t>উন্নত আধুনিক পদার্থবিজ্ঞান সংশ্লেষণ ও তাত্ত্বিক প্রমাণ (Modern Physics Synthesis)</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -5883,31 +5616,25 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>##PRESET:photoelectric-setup[size:medium]##
-[সমস্যা 44: আলোকতড়িৎ ক্রিয়া ও নিবৃত্তি বিভব]
-##PRESET:photoelectric-setup[size:medium]##
-একটি ধাতব পৃষ্ঠের কার্য অপেক্ষক $W_0 = 6.2\text{ eV}$। ধাতুটির ওপর $\lambda = 2000\text{ \AA}$ তরঙ্গদৈর্ঘ্যের অতিবেগুনি রশ্মি আপতিত হলে নিঃসৃত ফোটো-ইলেকট্রনের সর্বোচ্চ গতিশক্তি ও নিবৃত্তি বিভব ($V_0$) কত?</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি ফোটনের তরঙ্গদৈর্ঘ্য $\lambda$। ফোটনটির ভরবেগ $p = h/\lambda$। দেখাও যে ফোটনের শক্তি $E = h f$ এর সাথে আইনস্টাইনের $E = p c$ সমীকরণ সম্পূর্ণ সঙ্গতিপূর্ণ।</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>##PRESET:photoelectric-setup[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 44)।</t>
+          <t>দ্য ব্রয়ের সমীকরণ $p = h/\lambda$ এবং তরঙ্গের মৌলিক সম্পর্ক $c = f \lambda$। আইনস্টাইনের ভরহীন কণার সমীকরণ $E = p c$ বসালে: $E = \left(\frac{h}{\lambda}\right)c = h \frac{c}{\lambda} = h f$, যা প্লাঙ্কের কোয়ান্টাম শক্তির সাথে সম্পূর্ণ ঐক্য প্রকাশ করে।</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 44</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+          <t>$E = p c = \left(\frac{h}{\lambda}\right)c = h\left(\frac{c}{\lambda}\right) = h f$</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5927,38 +5654,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ডি-ব্রগলী তরঙ্গদৈর্ঘ্য ও ইলেকট্রনের বেগ (সমস্যা 45)</t>
+          <t>উন্নত আধুনিক পদার্থবিজ্ঞান সংশ্লেষণ ও তাত্ত্বিক প্রমাণ (Modern Physics Synthesis)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>[সমস্যা 45: ডি-ব্রগলী তরঙ্গদৈর্ঘ্য ও ইলেকট্রনের বেগ]
-একটি ইলেকট্রনকে $V = 700\text{ V}$ বিভব পার্থক্যের মধ্য দিয়ে ত্বরান্বিত করা হলো। ইলেকট্রনটির সাথে সংশ্লিষ্ট ডি-ব্রগলী তরঙ্গদৈর্ঘ্য ($\lambda = \frac{12.27}{\sqrt{V}}\text{ \AA}$) কত?</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি ইলেকট্রন মাইক্রোস্কোপে ইলেকট্রনকে $V = 50.0\text{ kV}$ বিভবে ত্বরাম্বিত করা হয়। এই ইলেকট্রনগুলোর দ্য ব্রয় তরঙ্গদৈর্ঘ্য দৃশ্যমান আলোর ($pprox 550\text{ nm}$) তুলনায় কত গুণ ক্ষুদ্র?</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 45)।</t>
+          <t>আপেক্ষিক সংশোধন সহ $50\text{ kV}$-এ $\lambda = \frac{1.227}{\sqrt{50000}}\text{ nm} \approx 0.00548\text{ nm} \approx 5.4\text{ pm}$। দৃশ্যমান আলোর তরঙ্গদৈর্ঘ্য $\lambda_{\text{light}} \approx 550\text{ nm}$। অনুপাত $= \frac{550}{0.00548} \approx 100365$ গুণ ক্ষুদ্র। তরঙ্গদৈর্ঘ্য এত ক্ষুদ্র হওয়ায় ইলেকট্রন মাইক্রোস্কোপে অপবর্তনজনিত সীমাবদ্ধতা অতিক্রম করে লক্ষ গুণ বিবর্ধন সম্ভব হয়।</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 45</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+          <t>ইলেকট্রন তরঙ্গদৈর্ঘ্য $\approx 0.00536\text{ nm} = 5.36\text{ pm}$ (দৃশ্যমান আলোর চেয়ে প্রায় ১,০০,০০০ গুণ ক্ষুদ্র)</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5978,12 +5705,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>কম্পটন সরণ ও ফোটন বিচ্ছুরণ (সমস্যা 46)</t>
+          <t>উন্নত আধুনিক পদার্থবিজ্ঞান সংশ্লেষণ ও তাত্ত্বিক প্রমাণ (Modern Physics Synthesis)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -5991,25 +5718,25 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>[সমস্যা 46: কম্পটন সরণ ও ফোটন বিচ্ছুরণ]
-একটি এক্স-রে ফোটন একটি স্থির ইলেকট্রনের সাথে সংঘর্ষে লিপ্ত হয়ে $\theta = 80^\circ$ কোণে বিক্ষিপ্ত হলো। ফোটনটির তরঙ্গদৈর্ঘ্যের কম্পটন বৃদ্ধি $\Delta\lambda = \frac{h}{m_0 c}(1 - \cos\theta)$ কত আর্মস্ট্রং?</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি ধাতুর কার্য-অপেক্ষক $W_0$। ধাতুর ওপর আপতিত আলোর তরঙ্গদৈর্ঘ্য অর্ধেক ($\lambda/2$) করা হলে নির্গত ইলেকট্রনের সর্বোচ্চ গতিশক্তি কি দ্বিগুণ হবে?</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 46)।</t>
+          <t>$K = \frac{hc}{\lambda} - W_0 \implies \frac{hc}{\lambda} = K + W_0$। তরঙ্গদৈর্ঘ্য অর্ধেক হলে নতুন গতিশক্তি $K' = \frac{hc}{\lambda/2} - W_0 = 2\left(\frac{hc}{\lambda}\right) - W_0 = 2(K + W_0) - W_0 = 2K + W_0$। যেহেতু $W_0 &gt; 0$, তাই নতুন গতিশক্তি আদি গতিশক্তির দ্বিগুণের চেয়েও বেশি হবে।</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 46</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+          <t>না, গতিশক্তি দ্বিগুণের চেয়েও বেশি বৃদ্ধি পাবে ($K' = 2K + W_0 &gt; 2K$)</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6029,38 +5756,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>এক্স-রে নলের কাট-অফ তরঙ্গদৈর্ঘ্য (সমস্যা 47)</t>
+          <t>উন্নত আধুনিক পদার্থবিজ্ঞান সংশ্লেষণ ও তাত্ত্বিক প্রমাণ (Modern Physics Synthesis)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>[সমস্যা 47: এক্স-রে নলের কাট-অফ তরঙ্গদৈর্ঘ্য]
-একটি কুলিজ নলে $V = 90\text{ kV}$ বিভব প্রযুক্ত থাকলে উৎপন্ন এক্স-রের ন্যূনতম তরঙ্গদৈর্ঘ্য (Cut-off wavelength, $\lambda_{min} = \frac{hc}{eV}$) কত?</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি স্থির অবস্থায় থাকা কণা ক্ষয়প্রাপ্ত হয়ে $m_1$ ও $m_2$ ভরের দুটি কণায় বিভক্ত হলো। ক্ষয়ের পর কণা দুটির ভরবেগ $p_1$ ও $p_2$-এর মান কী হবে?</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 47)।</t>
+          <t>রৈখিক ভরবেগের নিত্যতা অনুসারে প্রারম্ভিক ভরবেগ শূন্য: $\vec{p}_{\text{initial}} = 0 \implies \vec{p}_1 + \vec{p}_2 = 0 \implies \vec{p}_1 = -\vec{p}_2$। সুতরাং উভয়ের ভরবেগের মান সম্পূর্ণ সমান এবং এরা পরস্পরের ঠিক ১৮০ ডিগ্রি বিপরীত দিকে ছিটকে যাবে।</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 47</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+          <t>ভরবেগ সমান ও বিপরীতমুখী হবে ($|\vec{p}_1| = |\vec{p}_2| = p$)</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6080,12 +5807,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>হাইজেনবার্গের অনিশ্চয়তা নীতি (সমস্যা 48)</t>
+          <t>উন্নত আধুনিক পদার্থবিজ্ঞান সংশ্লেষণ ও তাত্ত্বিক প্রমাণ (Modern Physics Synthesis)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -6093,25 +5820,25 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>[সমস্যা 48: হাইজেনবার্গের অনিশ্চয়তা নীতি]
-একটি গতিশীল ইলেকট্রনের অবস্থান পরিমাপে অনিশ্চয়তা $\Delta x = 0.6\text{ nm}$। হাইজেনবার্গের অনিশ্চয়তা নীতিানুসারে ইলেকট্রনটির ভরবেগ পরিমাপে ন্যূনতম অনিশ্চয়তা কত?</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি ইলেকট্রন $v = 0.99 c$ বেগে গতিশীল। ইলেকট্রনটির আপেক্ষিক ভরবেগ এবং চিরায়ত (Classical) ভরবেগের শতকরা অনুপাত কত?</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 48)।</t>
+          <t>$\gamma = \frac{1}{\sqrt{1 - 0.99^2}} = \frac{1}{\sqrt{1 - 0.9801}} = \frac{1}{\sqrt{0.0199}} \approx \frac{1}{0.14107} \approx 7.0888$। আপেক্ষিক ভরবেগ $p_{\text{rel}} = \gamma m_0 v = 7.089 p_{\text{classical}}$। শতকরা মান $= 708.9\%$।</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 48</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+          <t>আপেক্ষিক ভরবেগ চিরায়ত ভরবেগের $708.9\%$ (প্রায় ৭.০৯ গুণ বেশি)</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6131,38 +5858,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>ভর ত্রুটি হতে উৎপন্ন শক্তির পরিমাণ (সমস্যা 49)</t>
+          <t>উন্নত আধুনিক পদার্থবিজ্ঞান সংশ্লেষণ ও তাত্ত্বিক প্রমাণ (Modern Physics Synthesis)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>[সমস্যা 49: ভর ত্রুটি হতে উৎপন্ন শক্তির পরিমাণ]
-একটি পারমাণবিক ফিশন বিক্রিয়ায় $1\text{ g}$ ভর সম্পূর্ণরূপে শক্তিতে রূপান্তরিত হলে আইনস্টাইনের সমীকরণ $E = mc^2$ অনুযায়ী কত জুল বা কিলোওয়াট-ঘণ্টা শক্তি নির্গত হবে?</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি ফোটনের সাথে সংঘর্ষে একটি মুক্ত ইলেকট্রন কি সম্পূর্ণ ফোটনটিকে শোষণ করে নিতে পারে? আপেক্ষিক ভরবেগ ও শক্তির সংরক্ষণশীলতার সাহায্যে প্রমাণ কর।</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 49)।</t>
+          <t>ধরি স্থির ইলেকট্রন ফোটন শোষণ করে $v$ বেগে চলে: শক্তি সংরক্ষণ $\implies hf + m_0 c^2 = \gamma m_0 c^2$, ভরবেগ সংরক্ষণ $\implies \frac{hf}{c} = \gamma m_0 v$। দুটি সমীকরণ হতে সমাধান করলে পাওয়া যায় $v = c$, যা অশূন্য ভরের কণার জন্য অসম্ভব। তাই সম্পূর্ণ শোষণ হতে হলে পরমাণুর নিউক্লিয়াসের আবদ্ধ বাঁধন প্রয়োজন হয় (যেমন আলোক তড়িৎ ক্রিয়া)।</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 49</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+          <t>না, শক্তি ও ভরবেগ যুগপৎ সংরক্ষিত থাকা অসম্ভব হওয়ায় একটি মুক্ত ইলেকট্রন কখনোই একটি ফোটনকে সম্পূর্ণ শোষণ করতে পারে না</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6182,12 +5909,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>সূচনা কম্পাঙ্ক ও কার্য-অপেক্ষক (সমস্যা 50)</t>
+          <t>উন্নত আধুনিক পদার্থবিজ্ঞান সংশ্লেষণ ও তাত্ত্বিক প্রমাণ (Modern Physics Synthesis)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -6195,25 +5922,25 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>[সমস্যা 50: সূচনা কম্পাঙ্ক ও কার্য-অপেক্ষক]
-সিজিয়াম ধাতুর সূচনা তরঙ্গদৈর্ঘ্য $\lambda_0 = 8500\text{ \AA}$। ধাতুটির কার্য-অপেক্ষক ($W_0 = hc/\lambda_0$) ইলেকট্রন-ভোল্ট (eV) এককে নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+সময় ও শক্তির জন্য হাইজেনবার্গের অনিশ্চয়তা নীতি: $\Delta E \cdot \Delta t \ge rac{\hbar}{2}$। একটি পরমাণুর উত্তেজিত অবস্থার আয়ুষ্কাল $	au pprox 1.0 	imes 10^{-8}\text{ s}$। নিঃসৃত বর্ণালী রেখার প্রাকৃতিক কম্পাঙ্ক অনিশ্চয়তা $\Delta f$ কত?</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>লরেন্টজ রূপান্তর, আইনস্টাইনের আলোকতড়িৎ সমীকরণ ও কোয়ান্টাম বলবিদ্যার সমীকরণ দ্বারা সমাধান (সমস্যা 50)।</t>
+          <t>$\Delta E \Delta t \ge \frac{h}{4\pi} \implies h \Delta f \Delta t \approx \frac{h}{4\pi} \implies \Delta f \approx \frac{1}{4\pi \Delta t} = \frac{1}{4\pi (1.0 \times 10^{-8}\text{ s})} = \frac{10^8}{4\pi} \approx 7.958 \times 10^6\text{ Hz} \approx 8.0\text{ MHz}$। এর কারণে বর্ণালী রেখা কখনোই অসীম তীক্ষ্ণ হয় না, এর একটি প্রাকৃতিক রেখা-প্রস্থ (Natural line width) থাকে।</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>আধুনিক পদার্থবিজ্ঞানের উত্তর 50</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+          <t>কম্পাঙ্ক অনিশ্চয়তা $\Delta f \approx 7.96 \times 10^6\text{ Hz} \approx 8.0\text{ MHz}$</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
